--- a/products-storage/11-bankrotstvo-genpodryadchika/04-reestr-dokumentov-i-dat-po-obektu.xlsx
+++ b/products-storage/11-bankrotstvo-genpodryadchika/04-reestr-dokumentov-i-dat-po-obektu.xlsx
@@ -1,18 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Объект и должник" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Реестр документов" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Итоги" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Пример заполнения" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объект и должник" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр документов" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пример заполнения" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Объект и должник'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Объект и должник'!$A$1:$C$39</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Реестр документов'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Реестр документов'!$A$1:$M$205</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Итоги'!$A$1:$C$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Пример заполнения'!$A$1:$M$22</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -571,7 +578,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -581,17 +588,17 @@
     <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Объект, должник и дата, к которой всё должно быть готово</t>
+          <t xml:space="preserve">Объект, должник и контрольные даты</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Заполните жёлтые ячейки. Синим — то, что вводите вы; чёрным — то, что считают формулы. Сведения берите из судебного акта и из публикации, а не из пересказа.</t>
+          <t xml:space="preserve">Внесите сведения из судебного акта и официальной публикации. Жёлтые ячейки предназначены для ввода, расчётные показатели формируются автоматически.</t>
         </is>
       </c>
     </row>
@@ -650,7 +657,7 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>По нему ставится наблюдение в источниках</t>
+          <t xml:space="preserve">Используйте ИНН для однозначной идентификации должника в публичных источниках.</t>
         </is>
       </c>
     </row>
@@ -768,14 +775,14 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Срок заявления требования — проверяете вы, а не файл</t>
+          <t xml:space="preserve">Определение срока заявления требования</t>
         </is>
       </c>
     </row>
     <row r="21" ht="78" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Числа срока в этом файле нет намеренно. Срок зависит от процедуры (наблюдение — ст. 71, внешнее управление — ст. 100, конкурсное производство — ст. 142 Закона о банкротстве), считается от даты публикации и меняется вместе с редакцией закона. Формула, прибавляющая зашитое число дней, устарела бы молча и при этом выглядела бы точной. Проверьте действующую редакцию названной статьи, отсчитайте срок от даты публикации, запишите полученную дату ниже и подтвердите её у юриста.</t>
+          <t>Определите применимую процедуру и срок по ст. 71, 100 или 142 Закона № 127-ФЗ; сверьте дату и источник публикации, поставьте контрольную дату.</t>
         </is>
       </c>
     </row>
@@ -792,7 +799,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="24.0" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Дата, до которой требование должно быть заявлено</t>
@@ -801,7 +808,7 @@
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Ваша запись по результату проверки. Поставьте напоминание заметно раньше этой даты</t>
+          <t xml:space="preserve">Укажите предельную дату по применимой процедуре и назначьте дату внутреннего контроля до её истечения.</t>
         </is>
       </c>
     </row>
@@ -814,7 +821,7 @@
       <c r="B25" s="4" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Фамилия и дата. «Проверено» без фамилии не выполняется</t>
+          <t xml:space="preserve">Фамилия ответственного, дата проверки и ссылка на источник.</t>
         </is>
       </c>
     </row>
@@ -825,8 +832,7 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>IF($B$24="","срок не проверен — заполните строки 23–25",IF($B$25="","дата записана, но не указано, кем и когда проверена",IF($B$24&lt;TODAY(),"дата по вашей записи прошла — файл «Что делать, если срок пропущен» и юрист сегодня","дней до вашей даты: "&amp;($B$24-TODAY()))))</f>
-        <v/>
+        <f>IF($B$24="","срок не проверен — заполните строки 23–25",IF($B$25="","дата записана, но не указано, кем и когда проверена",IF($B$24&lt;TODAY(),"Указанная контрольная дата истекла: проверьте срок и процессуальный порядок по файлу 09.","Дней до контрольной даты: "&amp;($B$24-TODAY()))))</f>
       </c>
       <c r="C27" s="9" t="n"/>
     </row>
@@ -850,7 +856,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="24.0" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Адрес для корреспонденции</t>
@@ -859,7 +865,7 @@
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Адрес, указанный в публикации. Письмо по другому адресу — это письмо, которое вы не направили</t>
+          <t xml:space="preserve">Адрес для корреспонденции из официальной публикации или судебного акта. Сохраните подтверждение направления.</t>
         </is>
       </c>
     </row>
@@ -892,28 +898,28 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Что этот лист не решает</t>
+          <t xml:space="preserve">Квалификация требования</t>
         </is>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Квалификацию требования — реестровое или текущий платёж — файл не делает и сделать не может: момент возникновения обязательства по оплате не всегда совпадает с датой акта. Колонка «Период» на листе реестра расставляет документы по датам, чтобы юристу было с чем работать, и не более того.</t>
+          <t xml:space="preserve">Сопоставьте даты возникновения обязательств с датой принятия заявления о банкротстве. Квалификацию требования определите по статье 5 Закона № 127-ФЗ и судебным материалам.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Прочитайте до того, как заполнять</t>
+          <t xml:space="preserve">Контроль перед заполнением</t>
         </is>
       </c>
     </row>
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Это рабочая таблица, а не юридическая консультация и не гарантия включения требования в реестр. Она приводит документы и даты в порядок — решения по ним принимает юрист по вашему делу. Пропущенный срок восстанавливается не всегда, а требование, поданное с ошибкой, теряет очередь. Сроков и ставок числом в файле нет намеренно: они меняются вместе с редакцией закона, а скачанная книга не обновляется — каждую дату вы проверяете сами на дату заполнения и подтверждаете у юриста.</t>
+          <t>Сверьте реестр, расчёт и опубликованные сведения с судебными актами. Заявление направляется в суд отдельно.</t>
         </is>
       </c>
     </row>
@@ -926,6 +932,7 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -934,7 +941,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -964,11 +971,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Жёлтые колонки заполняете вы, по одной строке на документ. Колонки «Период» и «Проверка» считаются сами. Заполняйте по ходу работ: в день публикации сведений времени на археологию уже не будет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>По каждой позиции внесите реквизиты и период. Колонки «Период» и «Проверка» показывают строки для дополнительной сверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26.4" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>№</t>
@@ -1016,7 +1023,7 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Где лежит оригинал</t>
+          <t xml:space="preserve">Место хранения оригинала</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
@@ -1055,8 +1062,7 @@
         <v/>
       </c>
       <c r="M4" s="13">
-        <f>IF($B4="","",IF(AND($E4&gt;0,LOWER($F4)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G4&lt;&gt;"",$I4=""),"направлено, но подтверждение направления не указано",IF($K4="","отметьте, идёт ли копия в пакет",IF($L4="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B4="","",IF(AND($E4&gt;0,LOWER($F4)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G4&lt;&gt;"",$I4=""),"направлено, но подтверждение направления не указано",IF($K4="","Отметьте включение копии в перечень приложений.",IF($L4="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="5">
@@ -1079,8 +1085,7 @@
         <v/>
       </c>
       <c r="M5" s="13">
-        <f>IF($B5="","",IF(AND($E5&gt;0,LOWER($F5)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G5&lt;&gt;"",$I5=""),"направлено, но подтверждение направления не указано",IF($K5="","отметьте, идёт ли копия в пакет",IF($L5="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B5="","",IF(AND($E5&gt;0,LOWER($F5)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G5&lt;&gt;"",$I5=""),"направлено, но подтверждение направления не указано",IF($K5="","Отметьте включение копии в перечень приложений.",IF($L5="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="6">
@@ -1103,8 +1108,7 @@
         <v/>
       </c>
       <c r="M6" s="13">
-        <f>IF($B6="","",IF(AND($E6&gt;0,LOWER($F6)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G6&lt;&gt;"",$I6=""),"направлено, но подтверждение направления не указано",IF($K6="","отметьте, идёт ли копия в пакет",IF($L6="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B6="","",IF(AND($E6&gt;0,LOWER($F6)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G6&lt;&gt;"",$I6=""),"направлено, но подтверждение направления не указано",IF($K6="","Отметьте включение копии в перечень приложений.",IF($L6="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="7">
@@ -1127,8 +1131,7 @@
         <v/>
       </c>
       <c r="M7" s="13">
-        <f>IF($B7="","",IF(AND($E7&gt;0,LOWER($F7)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G7&lt;&gt;"",$I7=""),"направлено, но подтверждение направления не указано",IF($K7="","отметьте, идёт ли копия в пакет",IF($L7="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B7="","",IF(AND($E7&gt;0,LOWER($F7)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G7&lt;&gt;"",$I7=""),"направлено, но подтверждение направления не указано",IF($K7="","Отметьте включение копии в перечень приложений.",IF($L7="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="8">
@@ -1151,8 +1154,7 @@
         <v/>
       </c>
       <c r="M8" s="13">
-        <f>IF($B8="","",IF(AND($E8&gt;0,LOWER($F8)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G8&lt;&gt;"",$I8=""),"направлено, но подтверждение направления не указано",IF($K8="","отметьте, идёт ли копия в пакет",IF($L8="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B8="","",IF(AND($E8&gt;0,LOWER($F8)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G8&lt;&gt;"",$I8=""),"направлено, но подтверждение направления не указано",IF($K8="","Отметьте включение копии в перечень приложений.",IF($L8="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="9">
@@ -1175,8 +1177,7 @@
         <v/>
       </c>
       <c r="M9" s="13">
-        <f>IF($B9="","",IF(AND($E9&gt;0,LOWER($F9)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G9&lt;&gt;"",$I9=""),"направлено, но подтверждение направления не указано",IF($K9="","отметьте, идёт ли копия в пакет",IF($L9="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B9="","",IF(AND($E9&gt;0,LOWER($F9)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G9&lt;&gt;"",$I9=""),"направлено, но подтверждение направления не указано",IF($K9="","Отметьте включение копии в перечень приложений.",IF($L9="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="10">
@@ -1199,8 +1200,7 @@
         <v/>
       </c>
       <c r="M10" s="13">
-        <f>IF($B10="","",IF(AND($E10&gt;0,LOWER($F10)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G10&lt;&gt;"",$I10=""),"направлено, но подтверждение направления не указано",IF($K10="","отметьте, идёт ли копия в пакет",IF($L10="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B10="","",IF(AND($E10&gt;0,LOWER($F10)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G10&lt;&gt;"",$I10=""),"направлено, но подтверждение направления не указано",IF($K10="","Отметьте включение копии в перечень приложений.",IF($L10="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="11">
@@ -1223,8 +1223,7 @@
         <v/>
       </c>
       <c r="M11" s="13">
-        <f>IF($B11="","",IF(AND($E11&gt;0,LOWER($F11)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G11&lt;&gt;"",$I11=""),"направлено, но подтверждение направления не указано",IF($K11="","отметьте, идёт ли копия в пакет",IF($L11="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B11="","",IF(AND($E11&gt;0,LOWER($F11)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G11&lt;&gt;"",$I11=""),"направлено, но подтверждение направления не указано",IF($K11="","Отметьте включение копии в перечень приложений.",IF($L11="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="12">
@@ -1247,8 +1246,7 @@
         <v/>
       </c>
       <c r="M12" s="13">
-        <f>IF($B12="","",IF(AND($E12&gt;0,LOWER($F12)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G12&lt;&gt;"",$I12=""),"направлено, но подтверждение направления не указано",IF($K12="","отметьте, идёт ли копия в пакет",IF($L12="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B12="","",IF(AND($E12&gt;0,LOWER($F12)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G12&lt;&gt;"",$I12=""),"направлено, но подтверждение направления не указано",IF($K12="","Отметьте включение копии в перечень приложений.",IF($L12="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="13">
@@ -1271,8 +1269,7 @@
         <v/>
       </c>
       <c r="M13" s="13">
-        <f>IF($B13="","",IF(AND($E13&gt;0,LOWER($F13)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G13&lt;&gt;"",$I13=""),"направлено, но подтверждение направления не указано",IF($K13="","отметьте, идёт ли копия в пакет",IF($L13="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B13="","",IF(AND($E13&gt;0,LOWER($F13)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G13&lt;&gt;"",$I13=""),"направлено, но подтверждение направления не указано",IF($K13="","Отметьте включение копии в перечень приложений.",IF($L13="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="14">
@@ -1295,8 +1292,7 @@
         <v/>
       </c>
       <c r="M14" s="13">
-        <f>IF($B14="","",IF(AND($E14&gt;0,LOWER($F14)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G14&lt;&gt;"",$I14=""),"направлено, но подтверждение направления не указано",IF($K14="","отметьте, идёт ли копия в пакет",IF($L14="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B14="","",IF(AND($E14&gt;0,LOWER($F14)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G14&lt;&gt;"",$I14=""),"направлено, но подтверждение направления не указано",IF($K14="","Отметьте включение копии в перечень приложений.",IF($L14="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="15">
@@ -1319,8 +1315,7 @@
         <v/>
       </c>
       <c r="M15" s="13">
-        <f>IF($B15="","",IF(AND($E15&gt;0,LOWER($F15)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G15&lt;&gt;"",$I15=""),"направлено, но подтверждение направления не указано",IF($K15="","отметьте, идёт ли копия в пакет",IF($L15="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B15="","",IF(AND($E15&gt;0,LOWER($F15)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G15&lt;&gt;"",$I15=""),"направлено, но подтверждение направления не указано",IF($K15="","Отметьте включение копии в перечень приложений.",IF($L15="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="16">
@@ -1343,8 +1338,7 @@
         <v/>
       </c>
       <c r="M16" s="13">
-        <f>IF($B16="","",IF(AND($E16&gt;0,LOWER($F16)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G16&lt;&gt;"",$I16=""),"направлено, но подтверждение направления не указано",IF($K16="","отметьте, идёт ли копия в пакет",IF($L16="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B16="","",IF(AND($E16&gt;0,LOWER($F16)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G16&lt;&gt;"",$I16=""),"направлено, но подтверждение направления не указано",IF($K16="","Отметьте включение копии в перечень приложений.",IF($L16="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="17">
@@ -1367,8 +1361,7 @@
         <v/>
       </c>
       <c r="M17" s="13">
-        <f>IF($B17="","",IF(AND($E17&gt;0,LOWER($F17)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G17&lt;&gt;"",$I17=""),"направлено, но подтверждение направления не указано",IF($K17="","отметьте, идёт ли копия в пакет",IF($L17="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B17="","",IF(AND($E17&gt;0,LOWER($F17)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G17&lt;&gt;"",$I17=""),"направлено, но подтверждение направления не указано",IF($K17="","Отметьте включение копии в перечень приложений.",IF($L17="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="18">
@@ -1391,8 +1384,7 @@
         <v/>
       </c>
       <c r="M18" s="13">
-        <f>IF($B18="","",IF(AND($E18&gt;0,LOWER($F18)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G18&lt;&gt;"",$I18=""),"направлено, но подтверждение направления не указано",IF($K18="","отметьте, идёт ли копия в пакет",IF($L18="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B18="","",IF(AND($E18&gt;0,LOWER($F18)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G18&lt;&gt;"",$I18=""),"направлено, но подтверждение направления не указано",IF($K18="","Отметьте включение копии в перечень приложений.",IF($L18="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="19">
@@ -1415,8 +1407,7 @@
         <v/>
       </c>
       <c r="M19" s="13">
-        <f>IF($B19="","",IF(AND($E19&gt;0,LOWER($F19)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G19&lt;&gt;"",$I19=""),"направлено, но подтверждение направления не указано",IF($K19="","отметьте, идёт ли копия в пакет",IF($L19="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B19="","",IF(AND($E19&gt;0,LOWER($F19)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G19&lt;&gt;"",$I19=""),"направлено, но подтверждение направления не указано",IF($K19="","Отметьте включение копии в перечень приложений.",IF($L19="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="20">
@@ -1439,8 +1430,7 @@
         <v/>
       </c>
       <c r="M20" s="13">
-        <f>IF($B20="","",IF(AND($E20&gt;0,LOWER($F20)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G20&lt;&gt;"",$I20=""),"направлено, но подтверждение направления не указано",IF($K20="","отметьте, идёт ли копия в пакет",IF($L20="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B20="","",IF(AND($E20&gt;0,LOWER($F20)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G20&lt;&gt;"",$I20=""),"направлено, но подтверждение направления не указано",IF($K20="","Отметьте включение копии в перечень приложений.",IF($L20="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="21">
@@ -1463,8 +1453,7 @@
         <v/>
       </c>
       <c r="M21" s="13">
-        <f>IF($B21="","",IF(AND($E21&gt;0,LOWER($F21)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G21&lt;&gt;"",$I21=""),"направлено, но подтверждение направления не указано",IF($K21="","отметьте, идёт ли копия в пакет",IF($L21="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B21="","",IF(AND($E21&gt;0,LOWER($F21)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G21&lt;&gt;"",$I21=""),"направлено, но подтверждение направления не указано",IF($K21="","Отметьте включение копии в перечень приложений.",IF($L21="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="22">
@@ -1487,8 +1476,7 @@
         <v/>
       </c>
       <c r="M22" s="13">
-        <f>IF($B22="","",IF(AND($E22&gt;0,LOWER($F22)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G22&lt;&gt;"",$I22=""),"направлено, но подтверждение направления не указано",IF($K22="","отметьте, идёт ли копия в пакет",IF($L22="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B22="","",IF(AND($E22&gt;0,LOWER($F22)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G22&lt;&gt;"",$I22=""),"направлено, но подтверждение направления не указано",IF($K22="","Отметьте включение копии в перечень приложений.",IF($L22="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="23">
@@ -1511,8 +1499,7 @@
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IF($B23="","",IF(AND($E23&gt;0,LOWER($F23)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G23&lt;&gt;"",$I23=""),"направлено, но подтверждение направления не указано",IF($K23="","отметьте, идёт ли копия в пакет",IF($L23="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B23="","",IF(AND($E23&gt;0,LOWER($F23)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G23&lt;&gt;"",$I23=""),"направлено, но подтверждение направления не указано",IF($K23="","Отметьте включение копии в перечень приложений.",IF($L23="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="24">
@@ -1535,8 +1522,7 @@
         <v/>
       </c>
       <c r="M24" s="13">
-        <f>IF($B24="","",IF(AND($E24&gt;0,LOWER($F24)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G24&lt;&gt;"",$I24=""),"направлено, но подтверждение направления не указано",IF($K24="","отметьте, идёт ли копия в пакет",IF($L24="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B24="","",IF(AND($E24&gt;0,LOWER($F24)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G24&lt;&gt;"",$I24=""),"направлено, но подтверждение направления не указано",IF($K24="","Отметьте включение копии в перечень приложений.",IF($L24="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="25">
@@ -1559,8 +1545,7 @@
         <v/>
       </c>
       <c r="M25" s="13">
-        <f>IF($B25="","",IF(AND($E25&gt;0,LOWER($F25)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G25&lt;&gt;"",$I25=""),"направлено, но подтверждение направления не указано",IF($K25="","отметьте, идёт ли копия в пакет",IF($L25="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B25="","",IF(AND($E25&gt;0,LOWER($F25)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G25&lt;&gt;"",$I25=""),"направлено, но подтверждение направления не указано",IF($K25="","Отметьте включение копии в перечень приложений.",IF($L25="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="26">
@@ -1583,8 +1568,7 @@
         <v/>
       </c>
       <c r="M26" s="13">
-        <f>IF($B26="","",IF(AND($E26&gt;0,LOWER($F26)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G26&lt;&gt;"",$I26=""),"направлено, но подтверждение направления не указано",IF($K26="","отметьте, идёт ли копия в пакет",IF($L26="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B26="","",IF(AND($E26&gt;0,LOWER($F26)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G26&lt;&gt;"",$I26=""),"направлено, но подтверждение направления не указано",IF($K26="","Отметьте включение копии в перечень приложений.",IF($L26="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="27">
@@ -1607,8 +1591,7 @@
         <v/>
       </c>
       <c r="M27" s="13">
-        <f>IF($B27="","",IF(AND($E27&gt;0,LOWER($F27)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G27&lt;&gt;"",$I27=""),"направлено, но подтверждение направления не указано",IF($K27="","отметьте, идёт ли копия в пакет",IF($L27="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B27="","",IF(AND($E27&gt;0,LOWER($F27)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G27&lt;&gt;"",$I27=""),"направлено, но подтверждение направления не указано",IF($K27="","Отметьте включение копии в перечень приложений.",IF($L27="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="28">
@@ -1631,8 +1614,7 @@
         <v/>
       </c>
       <c r="M28" s="13">
-        <f>IF($B28="","",IF(AND($E28&gt;0,LOWER($F28)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G28&lt;&gt;"",$I28=""),"направлено, но подтверждение направления не указано",IF($K28="","отметьте, идёт ли копия в пакет",IF($L28="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B28="","",IF(AND($E28&gt;0,LOWER($F28)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G28&lt;&gt;"",$I28=""),"направлено, но подтверждение направления не указано",IF($K28="","Отметьте включение копии в перечень приложений.",IF($L28="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="29">
@@ -1655,8 +1637,7 @@
         <v/>
       </c>
       <c r="M29" s="13">
-        <f>IF($B29="","",IF(AND($E29&gt;0,LOWER($F29)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G29&lt;&gt;"",$I29=""),"направлено, но подтверждение направления не указано",IF($K29="","отметьте, идёт ли копия в пакет",IF($L29="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B29="","",IF(AND($E29&gt;0,LOWER($F29)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G29&lt;&gt;"",$I29=""),"направлено, но подтверждение направления не указано",IF($K29="","Отметьте включение копии в перечень приложений.",IF($L29="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="30">
@@ -1679,8 +1660,7 @@
         <v/>
       </c>
       <c r="M30" s="13">
-        <f>IF($B30="","",IF(AND($E30&gt;0,LOWER($F30)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G30&lt;&gt;"",$I30=""),"направлено, но подтверждение направления не указано",IF($K30="","отметьте, идёт ли копия в пакет",IF($L30="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B30="","",IF(AND($E30&gt;0,LOWER($F30)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G30&lt;&gt;"",$I30=""),"направлено, но подтверждение направления не указано",IF($K30="","Отметьте включение копии в перечень приложений.",IF($L30="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="31">
@@ -1703,8 +1683,7 @@
         <v/>
       </c>
       <c r="M31" s="13">
-        <f>IF($B31="","",IF(AND($E31&gt;0,LOWER($F31)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G31&lt;&gt;"",$I31=""),"направлено, но подтверждение направления не указано",IF($K31="","отметьте, идёт ли копия в пакет",IF($L31="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B31="","",IF(AND($E31&gt;0,LOWER($F31)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G31&lt;&gt;"",$I31=""),"направлено, но подтверждение направления не указано",IF($K31="","Отметьте включение копии в перечень приложений.",IF($L31="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="32">
@@ -1727,8 +1706,7 @@
         <v/>
       </c>
       <c r="M32" s="13">
-        <f>IF($B32="","",IF(AND($E32&gt;0,LOWER($F32)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G32&lt;&gt;"",$I32=""),"направлено, но подтверждение направления не указано",IF($K32="","отметьте, идёт ли копия в пакет",IF($L32="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B32="","",IF(AND($E32&gt;0,LOWER($F32)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G32&lt;&gt;"",$I32=""),"направлено, но подтверждение направления не указано",IF($K32="","Отметьте включение копии в перечень приложений.",IF($L32="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="33">
@@ -1751,8 +1729,7 @@
         <v/>
       </c>
       <c r="M33" s="13">
-        <f>IF($B33="","",IF(AND($E33&gt;0,LOWER($F33)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G33&lt;&gt;"",$I33=""),"направлено, но подтверждение направления не указано",IF($K33="","отметьте, идёт ли копия в пакет",IF($L33="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B33="","",IF(AND($E33&gt;0,LOWER($F33)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G33&lt;&gt;"",$I33=""),"направлено, но подтверждение направления не указано",IF($K33="","Отметьте включение копии в перечень приложений.",IF($L33="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="34">
@@ -1775,8 +1752,7 @@
         <v/>
       </c>
       <c r="M34" s="13">
-        <f>IF($B34="","",IF(AND($E34&gt;0,LOWER($F34)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G34&lt;&gt;"",$I34=""),"направлено, но подтверждение направления не указано",IF($K34="","отметьте, идёт ли копия в пакет",IF($L34="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B34="","",IF(AND($E34&gt;0,LOWER($F34)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G34&lt;&gt;"",$I34=""),"направлено, но подтверждение направления не указано",IF($K34="","Отметьте включение копии в перечень приложений.",IF($L34="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="35">
@@ -1799,8 +1775,7 @@
         <v/>
       </c>
       <c r="M35" s="13">
-        <f>IF($B35="","",IF(AND($E35&gt;0,LOWER($F35)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G35&lt;&gt;"",$I35=""),"направлено, но подтверждение направления не указано",IF($K35="","отметьте, идёт ли копия в пакет",IF($L35="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B35="","",IF(AND($E35&gt;0,LOWER($F35)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G35&lt;&gt;"",$I35=""),"направлено, но подтверждение направления не указано",IF($K35="","Отметьте включение копии в перечень приложений.",IF($L35="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="36">
@@ -1823,8 +1798,7 @@
         <v/>
       </c>
       <c r="M36" s="13">
-        <f>IF($B36="","",IF(AND($E36&gt;0,LOWER($F36)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G36&lt;&gt;"",$I36=""),"направлено, но подтверждение направления не указано",IF($K36="","отметьте, идёт ли копия в пакет",IF($L36="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B36="","",IF(AND($E36&gt;0,LOWER($F36)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G36&lt;&gt;"",$I36=""),"направлено, но подтверждение направления не указано",IF($K36="","Отметьте включение копии в перечень приложений.",IF($L36="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="37">
@@ -1847,8 +1821,7 @@
         <v/>
       </c>
       <c r="M37" s="13">
-        <f>IF($B37="","",IF(AND($E37&gt;0,LOWER($F37)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G37&lt;&gt;"",$I37=""),"направлено, но подтверждение направления не указано",IF($K37="","отметьте, идёт ли копия в пакет",IF($L37="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B37="","",IF(AND($E37&gt;0,LOWER($F37)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G37&lt;&gt;"",$I37=""),"направлено, но подтверждение направления не указано",IF($K37="","Отметьте включение копии в перечень приложений.",IF($L37="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="38">
@@ -1871,8 +1844,7 @@
         <v/>
       </c>
       <c r="M38" s="13">
-        <f>IF($B38="","",IF(AND($E38&gt;0,LOWER($F38)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G38&lt;&gt;"",$I38=""),"направлено, но подтверждение направления не указано",IF($K38="","отметьте, идёт ли копия в пакет",IF($L38="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B38="","",IF(AND($E38&gt;0,LOWER($F38)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G38&lt;&gt;"",$I38=""),"направлено, но подтверждение направления не указано",IF($K38="","Отметьте включение копии в перечень приложений.",IF($L38="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="39">
@@ -1895,8 +1867,7 @@
         <v/>
       </c>
       <c r="M39" s="13">
-        <f>IF($B39="","",IF(AND($E39&gt;0,LOWER($F39)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G39&lt;&gt;"",$I39=""),"направлено, но подтверждение направления не указано",IF($K39="","отметьте, идёт ли копия в пакет",IF($L39="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B39="","",IF(AND($E39&gt;0,LOWER($F39)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G39&lt;&gt;"",$I39=""),"направлено, но подтверждение направления не указано",IF($K39="","Отметьте включение копии в перечень приложений.",IF($L39="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="40">
@@ -1919,8 +1890,7 @@
         <v/>
       </c>
       <c r="M40" s="13">
-        <f>IF($B40="","",IF(AND($E40&gt;0,LOWER($F40)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G40&lt;&gt;"",$I40=""),"направлено, но подтверждение направления не указано",IF($K40="","отметьте, идёт ли копия в пакет",IF($L40="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B40="","",IF(AND($E40&gt;0,LOWER($F40)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G40&lt;&gt;"",$I40=""),"направлено, но подтверждение направления не указано",IF($K40="","Отметьте включение копии в перечень приложений.",IF($L40="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="41">
@@ -1943,8 +1913,7 @@
         <v/>
       </c>
       <c r="M41" s="13">
-        <f>IF($B41="","",IF(AND($E41&gt;0,LOWER($F41)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G41&lt;&gt;"",$I41=""),"направлено, но подтверждение направления не указано",IF($K41="","отметьте, идёт ли копия в пакет",IF($L41="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B41="","",IF(AND($E41&gt;0,LOWER($F41)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G41&lt;&gt;"",$I41=""),"направлено, но подтверждение направления не указано",IF($K41="","Отметьте включение копии в перечень приложений.",IF($L41="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="42">
@@ -1967,8 +1936,7 @@
         <v/>
       </c>
       <c r="M42" s="13">
-        <f>IF($B42="","",IF(AND($E42&gt;0,LOWER($F42)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G42&lt;&gt;"",$I42=""),"направлено, но подтверждение направления не указано",IF($K42="","отметьте, идёт ли копия в пакет",IF($L42="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B42="","",IF(AND($E42&gt;0,LOWER($F42)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G42&lt;&gt;"",$I42=""),"направлено, но подтверждение направления не указано",IF($K42="","Отметьте включение копии в перечень приложений.",IF($L42="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="43">
@@ -1991,8 +1959,7 @@
         <v/>
       </c>
       <c r="M43" s="13">
-        <f>IF($B43="","",IF(AND($E43&gt;0,LOWER($F43)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G43&lt;&gt;"",$I43=""),"направлено, но подтверждение направления не указано",IF($K43="","отметьте, идёт ли копия в пакет",IF($L43="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B43="","",IF(AND($E43&gt;0,LOWER($F43)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G43&lt;&gt;"",$I43=""),"направлено, но подтверждение направления не указано",IF($K43="","Отметьте включение копии в перечень приложений.",IF($L43="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="44">
@@ -2015,8 +1982,7 @@
         <v/>
       </c>
       <c r="M44" s="13">
-        <f>IF($B44="","",IF(AND($E44&gt;0,LOWER($F44)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G44&lt;&gt;"",$I44=""),"направлено, но подтверждение направления не указано",IF($K44="","отметьте, идёт ли копия в пакет",IF($L44="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B44="","",IF(AND($E44&gt;0,LOWER($F44)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G44&lt;&gt;"",$I44=""),"направлено, но подтверждение направления не указано",IF($K44="","Отметьте включение копии в перечень приложений.",IF($L44="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="45">
@@ -2039,8 +2005,7 @@
         <v/>
       </c>
       <c r="M45" s="13">
-        <f>IF($B45="","",IF(AND($E45&gt;0,LOWER($F45)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G45&lt;&gt;"",$I45=""),"направлено, но подтверждение направления не указано",IF($K45="","отметьте, идёт ли копия в пакет",IF($L45="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B45="","",IF(AND($E45&gt;0,LOWER($F45)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G45&lt;&gt;"",$I45=""),"направлено, но подтверждение направления не указано",IF($K45="","Отметьте включение копии в перечень приложений.",IF($L45="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="46">
@@ -2063,8 +2028,7 @@
         <v/>
       </c>
       <c r="M46" s="13">
-        <f>IF($B46="","",IF(AND($E46&gt;0,LOWER($F46)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G46&lt;&gt;"",$I46=""),"направлено, но подтверждение направления не указано",IF($K46="","отметьте, идёт ли копия в пакет",IF($L46="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B46="","",IF(AND($E46&gt;0,LOWER($F46)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G46&lt;&gt;"",$I46=""),"направлено, но подтверждение направления не указано",IF($K46="","Отметьте включение копии в перечень приложений.",IF($L46="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="47">
@@ -2087,8 +2051,7 @@
         <v/>
       </c>
       <c r="M47" s="13">
-        <f>IF($B47="","",IF(AND($E47&gt;0,LOWER($F47)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G47&lt;&gt;"",$I47=""),"направлено, но подтверждение направления не указано",IF($K47="","отметьте, идёт ли копия в пакет",IF($L47="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B47="","",IF(AND($E47&gt;0,LOWER($F47)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G47&lt;&gt;"",$I47=""),"направлено, но подтверждение направления не указано",IF($K47="","Отметьте включение копии в перечень приложений.",IF($L47="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="48">
@@ -2111,8 +2074,7 @@
         <v/>
       </c>
       <c r="M48" s="13">
-        <f>IF($B48="","",IF(AND($E48&gt;0,LOWER($F48)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G48&lt;&gt;"",$I48=""),"направлено, но подтверждение направления не указано",IF($K48="","отметьте, идёт ли копия в пакет",IF($L48="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B48="","",IF(AND($E48&gt;0,LOWER($F48)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G48&lt;&gt;"",$I48=""),"направлено, но подтверждение направления не указано",IF($K48="","Отметьте включение копии в перечень приложений.",IF($L48="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="49">
@@ -2135,8 +2097,7 @@
         <v/>
       </c>
       <c r="M49" s="13">
-        <f>IF($B49="","",IF(AND($E49&gt;0,LOWER($F49)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G49&lt;&gt;"",$I49=""),"направлено, но подтверждение направления не указано",IF($K49="","отметьте, идёт ли копия в пакет",IF($L49="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B49="","",IF(AND($E49&gt;0,LOWER($F49)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G49&lt;&gt;"",$I49=""),"направлено, но подтверждение направления не указано",IF($K49="","Отметьте включение копии в перечень приложений.",IF($L49="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="50">
@@ -2159,8 +2120,7 @@
         <v/>
       </c>
       <c r="M50" s="13">
-        <f>IF($B50="","",IF(AND($E50&gt;0,LOWER($F50)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G50&lt;&gt;"",$I50=""),"направлено, но подтверждение направления не указано",IF($K50="","отметьте, идёт ли копия в пакет",IF($L50="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B50="","",IF(AND($E50&gt;0,LOWER($F50)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G50&lt;&gt;"",$I50=""),"направлено, но подтверждение направления не указано",IF($K50="","Отметьте включение копии в перечень приложений.",IF($L50="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="51">
@@ -2183,8 +2143,7 @@
         <v/>
       </c>
       <c r="M51" s="13">
-        <f>IF($B51="","",IF(AND($E51&gt;0,LOWER($F51)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G51&lt;&gt;"",$I51=""),"направлено, но подтверждение направления не указано",IF($K51="","отметьте, идёт ли копия в пакет",IF($L51="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B51="","",IF(AND($E51&gt;0,LOWER($F51)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G51&lt;&gt;"",$I51=""),"направлено, но подтверждение направления не указано",IF($K51="","Отметьте включение копии в перечень приложений.",IF($L51="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="52">
@@ -2207,8 +2166,7 @@
         <v/>
       </c>
       <c r="M52" s="13">
-        <f>IF($B52="","",IF(AND($E52&gt;0,LOWER($F52)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G52&lt;&gt;"",$I52=""),"направлено, но подтверждение направления не указано",IF($K52="","отметьте, идёт ли копия в пакет",IF($L52="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B52="","",IF(AND($E52&gt;0,LOWER($F52)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G52&lt;&gt;"",$I52=""),"направлено, но подтверждение направления не указано",IF($K52="","Отметьте включение копии в перечень приложений.",IF($L52="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="53">
@@ -2231,8 +2189,7 @@
         <v/>
       </c>
       <c r="M53" s="13">
-        <f>IF($B53="","",IF(AND($E53&gt;0,LOWER($F53)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G53&lt;&gt;"",$I53=""),"направлено, но подтверждение направления не указано",IF($K53="","отметьте, идёт ли копия в пакет",IF($L53="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B53="","",IF(AND($E53&gt;0,LOWER($F53)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G53&lt;&gt;"",$I53=""),"направлено, но подтверждение направления не указано",IF($K53="","Отметьте включение копии в перечень приложений.",IF($L53="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="54">
@@ -2255,8 +2212,7 @@
         <v/>
       </c>
       <c r="M54" s="13">
-        <f>IF($B54="","",IF(AND($E54&gt;0,LOWER($F54)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G54&lt;&gt;"",$I54=""),"направлено, но подтверждение направления не указано",IF($K54="","отметьте, идёт ли копия в пакет",IF($L54="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B54="","",IF(AND($E54&gt;0,LOWER($F54)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G54&lt;&gt;"",$I54=""),"направлено, но подтверждение направления не указано",IF($K54="","Отметьте включение копии в перечень приложений.",IF($L54="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="55">
@@ -2279,8 +2235,7 @@
         <v/>
       </c>
       <c r="M55" s="13">
-        <f>IF($B55="","",IF(AND($E55&gt;0,LOWER($F55)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G55&lt;&gt;"",$I55=""),"направлено, но подтверждение направления не указано",IF($K55="","отметьте, идёт ли копия в пакет",IF($L55="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B55="","",IF(AND($E55&gt;0,LOWER($F55)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G55&lt;&gt;"",$I55=""),"направлено, но подтверждение направления не указано",IF($K55="","Отметьте включение копии в перечень приложений.",IF($L55="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="56">
@@ -2303,8 +2258,7 @@
         <v/>
       </c>
       <c r="M56" s="13">
-        <f>IF($B56="","",IF(AND($E56&gt;0,LOWER($F56)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G56&lt;&gt;"",$I56=""),"направлено, но подтверждение направления не указано",IF($K56="","отметьте, идёт ли копия в пакет",IF($L56="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B56="","",IF(AND($E56&gt;0,LOWER($F56)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G56&lt;&gt;"",$I56=""),"направлено, но подтверждение направления не указано",IF($K56="","Отметьте включение копии в перечень приложений.",IF($L56="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="57">
@@ -2327,8 +2281,7 @@
         <v/>
       </c>
       <c r="M57" s="13">
-        <f>IF($B57="","",IF(AND($E57&gt;0,LOWER($F57)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G57&lt;&gt;"",$I57=""),"направлено, но подтверждение направления не указано",IF($K57="","отметьте, идёт ли копия в пакет",IF($L57="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B57="","",IF(AND($E57&gt;0,LOWER($F57)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G57&lt;&gt;"",$I57=""),"направлено, но подтверждение направления не указано",IF($K57="","Отметьте включение копии в перечень приложений.",IF($L57="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="58">
@@ -2351,8 +2304,7 @@
         <v/>
       </c>
       <c r="M58" s="13">
-        <f>IF($B58="","",IF(AND($E58&gt;0,LOWER($F58)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G58&lt;&gt;"",$I58=""),"направлено, но подтверждение направления не указано",IF($K58="","отметьте, идёт ли копия в пакет",IF($L58="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B58="","",IF(AND($E58&gt;0,LOWER($F58)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G58&lt;&gt;"",$I58=""),"направлено, но подтверждение направления не указано",IF($K58="","Отметьте включение копии в перечень приложений.",IF($L58="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="59">
@@ -2375,8 +2327,7 @@
         <v/>
       </c>
       <c r="M59" s="13">
-        <f>IF($B59="","",IF(AND($E59&gt;0,LOWER($F59)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G59&lt;&gt;"",$I59=""),"направлено, но подтверждение направления не указано",IF($K59="","отметьте, идёт ли копия в пакет",IF($L59="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B59="","",IF(AND($E59&gt;0,LOWER($F59)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G59&lt;&gt;"",$I59=""),"направлено, но подтверждение направления не указано",IF($K59="","Отметьте включение копии в перечень приложений.",IF($L59="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="60">
@@ -2399,8 +2350,7 @@
         <v/>
       </c>
       <c r="M60" s="13">
-        <f>IF($B60="","",IF(AND($E60&gt;0,LOWER($F60)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G60&lt;&gt;"",$I60=""),"направлено, но подтверждение направления не указано",IF($K60="","отметьте, идёт ли копия в пакет",IF($L60="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B60="","",IF(AND($E60&gt;0,LOWER($F60)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G60&lt;&gt;"",$I60=""),"направлено, но подтверждение направления не указано",IF($K60="","Отметьте включение копии в перечень приложений.",IF($L60="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="61">
@@ -2423,8 +2373,7 @@
         <v/>
       </c>
       <c r="M61" s="13">
-        <f>IF($B61="","",IF(AND($E61&gt;0,LOWER($F61)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G61&lt;&gt;"",$I61=""),"направлено, но подтверждение направления не указано",IF($K61="","отметьте, идёт ли копия в пакет",IF($L61="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B61="","",IF(AND($E61&gt;0,LOWER($F61)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G61&lt;&gt;"",$I61=""),"направлено, но подтверждение направления не указано",IF($K61="","Отметьте включение копии в перечень приложений.",IF($L61="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="62">
@@ -2447,8 +2396,7 @@
         <v/>
       </c>
       <c r="M62" s="13">
-        <f>IF($B62="","",IF(AND($E62&gt;0,LOWER($F62)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G62&lt;&gt;"",$I62=""),"направлено, но подтверждение направления не указано",IF($K62="","отметьте, идёт ли копия в пакет",IF($L62="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B62="","",IF(AND($E62&gt;0,LOWER($F62)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G62&lt;&gt;"",$I62=""),"направлено, но подтверждение направления не указано",IF($K62="","Отметьте включение копии в перечень приложений.",IF($L62="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="63">
@@ -2471,8 +2419,7 @@
         <v/>
       </c>
       <c r="M63" s="13">
-        <f>IF($B63="","",IF(AND($E63&gt;0,LOWER($F63)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G63&lt;&gt;"",$I63=""),"направлено, но подтверждение направления не указано",IF($K63="","отметьте, идёт ли копия в пакет",IF($L63="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B63="","",IF(AND($E63&gt;0,LOWER($F63)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G63&lt;&gt;"",$I63=""),"направлено, но подтверждение направления не указано",IF($K63="","Отметьте включение копии в перечень приложений.",IF($L63="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="64">
@@ -2495,8 +2442,7 @@
         <v/>
       </c>
       <c r="M64" s="13">
-        <f>IF($B64="","",IF(AND($E64&gt;0,LOWER($F64)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G64&lt;&gt;"",$I64=""),"направлено, но подтверждение направления не указано",IF($K64="","отметьте, идёт ли копия в пакет",IF($L64="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B64="","",IF(AND($E64&gt;0,LOWER($F64)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G64&lt;&gt;"",$I64=""),"направлено, но подтверждение направления не указано",IF($K64="","Отметьте включение копии в перечень приложений.",IF($L64="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="65">
@@ -2519,8 +2465,7 @@
         <v/>
       </c>
       <c r="M65" s="13">
-        <f>IF($B65="","",IF(AND($E65&gt;0,LOWER($F65)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G65&lt;&gt;"",$I65=""),"направлено, но подтверждение направления не указано",IF($K65="","отметьте, идёт ли копия в пакет",IF($L65="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B65="","",IF(AND($E65&gt;0,LOWER($F65)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G65&lt;&gt;"",$I65=""),"направлено, но подтверждение направления не указано",IF($K65="","Отметьте включение копии в перечень приложений.",IF($L65="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="66">
@@ -2543,8 +2488,7 @@
         <v/>
       </c>
       <c r="M66" s="13">
-        <f>IF($B66="","",IF(AND($E66&gt;0,LOWER($F66)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G66&lt;&gt;"",$I66=""),"направлено, но подтверждение направления не указано",IF($K66="","отметьте, идёт ли копия в пакет",IF($L66="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B66="","",IF(AND($E66&gt;0,LOWER($F66)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G66&lt;&gt;"",$I66=""),"направлено, но подтверждение направления не указано",IF($K66="","Отметьте включение копии в перечень приложений.",IF($L66="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="67">
@@ -2567,8 +2511,7 @@
         <v/>
       </c>
       <c r="M67" s="13">
-        <f>IF($B67="","",IF(AND($E67&gt;0,LOWER($F67)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G67&lt;&gt;"",$I67=""),"направлено, но подтверждение направления не указано",IF($K67="","отметьте, идёт ли копия в пакет",IF($L67="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B67="","",IF(AND($E67&gt;0,LOWER($F67)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G67&lt;&gt;"",$I67=""),"направлено, но подтверждение направления не указано",IF($K67="","Отметьте включение копии в перечень приложений.",IF($L67="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="68">
@@ -2591,8 +2534,7 @@
         <v/>
       </c>
       <c r="M68" s="13">
-        <f>IF($B68="","",IF(AND($E68&gt;0,LOWER($F68)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G68&lt;&gt;"",$I68=""),"направлено, но подтверждение направления не указано",IF($K68="","отметьте, идёт ли копия в пакет",IF($L68="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B68="","",IF(AND($E68&gt;0,LOWER($F68)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G68&lt;&gt;"",$I68=""),"направлено, но подтверждение направления не указано",IF($K68="","Отметьте включение копии в перечень приложений.",IF($L68="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="69">
@@ -2615,8 +2557,7 @@
         <v/>
       </c>
       <c r="M69" s="13">
-        <f>IF($B69="","",IF(AND($E69&gt;0,LOWER($F69)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G69&lt;&gt;"",$I69=""),"направлено, но подтверждение направления не указано",IF($K69="","отметьте, идёт ли копия в пакет",IF($L69="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B69="","",IF(AND($E69&gt;0,LOWER($F69)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G69&lt;&gt;"",$I69=""),"направлено, но подтверждение направления не указано",IF($K69="","Отметьте включение копии в перечень приложений.",IF($L69="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="70">
@@ -2639,8 +2580,7 @@
         <v/>
       </c>
       <c r="M70" s="13">
-        <f>IF($B70="","",IF(AND($E70&gt;0,LOWER($F70)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G70&lt;&gt;"",$I70=""),"направлено, но подтверждение направления не указано",IF($K70="","отметьте, идёт ли копия в пакет",IF($L70="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B70="","",IF(AND($E70&gt;0,LOWER($F70)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G70&lt;&gt;"",$I70=""),"направлено, но подтверждение направления не указано",IF($K70="","Отметьте включение копии в перечень приложений.",IF($L70="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="71">
@@ -2663,8 +2603,7 @@
         <v/>
       </c>
       <c r="M71" s="13">
-        <f>IF($B71="","",IF(AND($E71&gt;0,LOWER($F71)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G71&lt;&gt;"",$I71=""),"направлено, но подтверждение направления не указано",IF($K71="","отметьте, идёт ли копия в пакет",IF($L71="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B71="","",IF(AND($E71&gt;0,LOWER($F71)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G71&lt;&gt;"",$I71=""),"направлено, но подтверждение направления не указано",IF($K71="","Отметьте включение копии в перечень приложений.",IF($L71="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="72">
@@ -2687,8 +2626,7 @@
         <v/>
       </c>
       <c r="M72" s="13">
-        <f>IF($B72="","",IF(AND($E72&gt;0,LOWER($F72)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G72&lt;&gt;"",$I72=""),"направлено, но подтверждение направления не указано",IF($K72="","отметьте, идёт ли копия в пакет",IF($L72="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B72="","",IF(AND($E72&gt;0,LOWER($F72)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G72&lt;&gt;"",$I72=""),"направлено, но подтверждение направления не указано",IF($K72="","Отметьте включение копии в перечень приложений.",IF($L72="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="73">
@@ -2711,8 +2649,7 @@
         <v/>
       </c>
       <c r="M73" s="13">
-        <f>IF($B73="","",IF(AND($E73&gt;0,LOWER($F73)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G73&lt;&gt;"",$I73=""),"направлено, но подтверждение направления не указано",IF($K73="","отметьте, идёт ли копия в пакет",IF($L73="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B73="","",IF(AND($E73&gt;0,LOWER($F73)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G73&lt;&gt;"",$I73=""),"направлено, но подтверждение направления не указано",IF($K73="","Отметьте включение копии в перечень приложений.",IF($L73="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="74">
@@ -2735,8 +2672,7 @@
         <v/>
       </c>
       <c r="M74" s="13">
-        <f>IF($B74="","",IF(AND($E74&gt;0,LOWER($F74)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G74&lt;&gt;"",$I74=""),"направлено, но подтверждение направления не указано",IF($K74="","отметьте, идёт ли копия в пакет",IF($L74="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B74="","",IF(AND($E74&gt;0,LOWER($F74)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G74&lt;&gt;"",$I74=""),"направлено, но подтверждение направления не указано",IF($K74="","Отметьте включение копии в перечень приложений.",IF($L74="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="75">
@@ -2759,8 +2695,7 @@
         <v/>
       </c>
       <c r="M75" s="13">
-        <f>IF($B75="","",IF(AND($E75&gt;0,LOWER($F75)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G75&lt;&gt;"",$I75=""),"направлено, но подтверждение направления не указано",IF($K75="","отметьте, идёт ли копия в пакет",IF($L75="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B75="","",IF(AND($E75&gt;0,LOWER($F75)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G75&lt;&gt;"",$I75=""),"направлено, но подтверждение направления не указано",IF($K75="","Отметьте включение копии в перечень приложений.",IF($L75="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="76">
@@ -2783,8 +2718,7 @@
         <v/>
       </c>
       <c r="M76" s="13">
-        <f>IF($B76="","",IF(AND($E76&gt;0,LOWER($F76)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G76&lt;&gt;"",$I76=""),"направлено, но подтверждение направления не указано",IF($K76="","отметьте, идёт ли копия в пакет",IF($L76="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B76="","",IF(AND($E76&gt;0,LOWER($F76)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G76&lt;&gt;"",$I76=""),"направлено, но подтверждение направления не указано",IF($K76="","Отметьте включение копии в перечень приложений.",IF($L76="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="77">
@@ -2807,8 +2741,7 @@
         <v/>
       </c>
       <c r="M77" s="13">
-        <f>IF($B77="","",IF(AND($E77&gt;0,LOWER($F77)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G77&lt;&gt;"",$I77=""),"направлено, но подтверждение направления не указано",IF($K77="","отметьте, идёт ли копия в пакет",IF($L77="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B77="","",IF(AND($E77&gt;0,LOWER($F77)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G77&lt;&gt;"",$I77=""),"направлено, но подтверждение направления не указано",IF($K77="","Отметьте включение копии в перечень приложений.",IF($L77="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="78">
@@ -2831,8 +2764,7 @@
         <v/>
       </c>
       <c r="M78" s="13">
-        <f>IF($B78="","",IF(AND($E78&gt;0,LOWER($F78)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G78&lt;&gt;"",$I78=""),"направлено, но подтверждение направления не указано",IF($K78="","отметьте, идёт ли копия в пакет",IF($L78="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B78="","",IF(AND($E78&gt;0,LOWER($F78)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G78&lt;&gt;"",$I78=""),"направлено, но подтверждение направления не указано",IF($K78="","Отметьте включение копии в перечень приложений.",IF($L78="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="79">
@@ -2855,8 +2787,7 @@
         <v/>
       </c>
       <c r="M79" s="13">
-        <f>IF($B79="","",IF(AND($E79&gt;0,LOWER($F79)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G79&lt;&gt;"",$I79=""),"направлено, но подтверждение направления не указано",IF($K79="","отметьте, идёт ли копия в пакет",IF($L79="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B79="","",IF(AND($E79&gt;0,LOWER($F79)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G79&lt;&gt;"",$I79=""),"направлено, но подтверждение направления не указано",IF($K79="","Отметьте включение копии в перечень приложений.",IF($L79="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="80">
@@ -2879,8 +2810,7 @@
         <v/>
       </c>
       <c r="M80" s="13">
-        <f>IF($B80="","",IF(AND($E80&gt;0,LOWER($F80)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G80&lt;&gt;"",$I80=""),"направлено, но подтверждение направления не указано",IF($K80="","отметьте, идёт ли копия в пакет",IF($L80="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B80="","",IF(AND($E80&gt;0,LOWER($F80)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G80&lt;&gt;"",$I80=""),"направлено, но подтверждение направления не указано",IF($K80="","Отметьте включение копии в перечень приложений.",IF($L80="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="81">
@@ -2903,8 +2833,7 @@
         <v/>
       </c>
       <c r="M81" s="13">
-        <f>IF($B81="","",IF(AND($E81&gt;0,LOWER($F81)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G81&lt;&gt;"",$I81=""),"направлено, но подтверждение направления не указано",IF($K81="","отметьте, идёт ли копия в пакет",IF($L81="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B81="","",IF(AND($E81&gt;0,LOWER($F81)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G81&lt;&gt;"",$I81=""),"направлено, но подтверждение направления не указано",IF($K81="","Отметьте включение копии в перечень приложений.",IF($L81="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="82">
@@ -2927,8 +2856,7 @@
         <v/>
       </c>
       <c r="M82" s="13">
-        <f>IF($B82="","",IF(AND($E82&gt;0,LOWER($F82)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G82&lt;&gt;"",$I82=""),"направлено, но подтверждение направления не указано",IF($K82="","отметьте, идёт ли копия в пакет",IF($L82="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B82="","",IF(AND($E82&gt;0,LOWER($F82)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G82&lt;&gt;"",$I82=""),"направлено, но подтверждение направления не указано",IF($K82="","Отметьте включение копии в перечень приложений.",IF($L82="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="83">
@@ -2951,8 +2879,7 @@
         <v/>
       </c>
       <c r="M83" s="13">
-        <f>IF($B83="","",IF(AND($E83&gt;0,LOWER($F83)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G83&lt;&gt;"",$I83=""),"направлено, но подтверждение направления не указано",IF($K83="","отметьте, идёт ли копия в пакет",IF($L83="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B83="","",IF(AND($E83&gt;0,LOWER($F83)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G83&lt;&gt;"",$I83=""),"направлено, но подтверждение направления не указано",IF($K83="","Отметьте включение копии в перечень приложений.",IF($L83="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="84">
@@ -2975,8 +2902,7 @@
         <v/>
       </c>
       <c r="M84" s="13">
-        <f>IF($B84="","",IF(AND($E84&gt;0,LOWER($F84)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G84&lt;&gt;"",$I84=""),"направлено, но подтверждение направления не указано",IF($K84="","отметьте, идёт ли копия в пакет",IF($L84="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B84="","",IF(AND($E84&gt;0,LOWER($F84)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G84&lt;&gt;"",$I84=""),"направлено, но подтверждение направления не указано",IF($K84="","Отметьте включение копии в перечень приложений.",IF($L84="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="85">
@@ -2999,8 +2925,7 @@
         <v/>
       </c>
       <c r="M85" s="13">
-        <f>IF($B85="","",IF(AND($E85&gt;0,LOWER($F85)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G85&lt;&gt;"",$I85=""),"направлено, но подтверждение направления не указано",IF($K85="","отметьте, идёт ли копия в пакет",IF($L85="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B85="","",IF(AND($E85&gt;0,LOWER($F85)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G85&lt;&gt;"",$I85=""),"направлено, но подтверждение направления не указано",IF($K85="","Отметьте включение копии в перечень приложений.",IF($L85="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="86">
@@ -3023,8 +2948,7 @@
         <v/>
       </c>
       <c r="M86" s="13">
-        <f>IF($B86="","",IF(AND($E86&gt;0,LOWER($F86)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G86&lt;&gt;"",$I86=""),"направлено, но подтверждение направления не указано",IF($K86="","отметьте, идёт ли копия в пакет",IF($L86="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B86="","",IF(AND($E86&gt;0,LOWER($F86)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G86&lt;&gt;"",$I86=""),"направлено, но подтверждение направления не указано",IF($K86="","Отметьте включение копии в перечень приложений.",IF($L86="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="87">
@@ -3047,8 +2971,7 @@
         <v/>
       </c>
       <c r="M87" s="13">
-        <f>IF($B87="","",IF(AND($E87&gt;0,LOWER($F87)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G87&lt;&gt;"",$I87=""),"направлено, но подтверждение направления не указано",IF($K87="","отметьте, идёт ли копия в пакет",IF($L87="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B87="","",IF(AND($E87&gt;0,LOWER($F87)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G87&lt;&gt;"",$I87=""),"направлено, но подтверждение направления не указано",IF($K87="","Отметьте включение копии в перечень приложений.",IF($L87="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="88">
@@ -3071,8 +2994,7 @@
         <v/>
       </c>
       <c r="M88" s="13">
-        <f>IF($B88="","",IF(AND($E88&gt;0,LOWER($F88)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G88&lt;&gt;"",$I88=""),"направлено, но подтверждение направления не указано",IF($K88="","отметьте, идёт ли копия в пакет",IF($L88="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B88="","",IF(AND($E88&gt;0,LOWER($F88)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G88&lt;&gt;"",$I88=""),"направлено, но подтверждение направления не указано",IF($K88="","Отметьте включение копии в перечень приложений.",IF($L88="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="89">
@@ -3095,8 +3017,7 @@
         <v/>
       </c>
       <c r="M89" s="13">
-        <f>IF($B89="","",IF(AND($E89&gt;0,LOWER($F89)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G89&lt;&gt;"",$I89=""),"направлено, но подтверждение направления не указано",IF($K89="","отметьте, идёт ли копия в пакет",IF($L89="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B89="","",IF(AND($E89&gt;0,LOWER($F89)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G89&lt;&gt;"",$I89=""),"направлено, но подтверждение направления не указано",IF($K89="","Отметьте включение копии в перечень приложений.",IF($L89="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="90">
@@ -3119,8 +3040,7 @@
         <v/>
       </c>
       <c r="M90" s="13">
-        <f>IF($B90="","",IF(AND($E90&gt;0,LOWER($F90)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G90&lt;&gt;"",$I90=""),"направлено, но подтверждение направления не указано",IF($K90="","отметьте, идёт ли копия в пакет",IF($L90="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B90="","",IF(AND($E90&gt;0,LOWER($F90)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G90&lt;&gt;"",$I90=""),"направлено, но подтверждение направления не указано",IF($K90="","Отметьте включение копии в перечень приложений.",IF($L90="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="91">
@@ -3143,8 +3063,7 @@
         <v/>
       </c>
       <c r="M91" s="13">
-        <f>IF($B91="","",IF(AND($E91&gt;0,LOWER($F91)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G91&lt;&gt;"",$I91=""),"направлено, но подтверждение направления не указано",IF($K91="","отметьте, идёт ли копия в пакет",IF($L91="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B91="","",IF(AND($E91&gt;0,LOWER($F91)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G91&lt;&gt;"",$I91=""),"направлено, но подтверждение направления не указано",IF($K91="","Отметьте включение копии в перечень приложений.",IF($L91="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="92">
@@ -3167,8 +3086,7 @@
         <v/>
       </c>
       <c r="M92" s="13">
-        <f>IF($B92="","",IF(AND($E92&gt;0,LOWER($F92)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G92&lt;&gt;"",$I92=""),"направлено, но подтверждение направления не указано",IF($K92="","отметьте, идёт ли копия в пакет",IF($L92="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B92="","",IF(AND($E92&gt;0,LOWER($F92)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G92&lt;&gt;"",$I92=""),"направлено, но подтверждение направления не указано",IF($K92="","Отметьте включение копии в перечень приложений.",IF($L92="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="93">
@@ -3191,8 +3109,7 @@
         <v/>
       </c>
       <c r="M93" s="13">
-        <f>IF($B93="","",IF(AND($E93&gt;0,LOWER($F93)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G93&lt;&gt;"",$I93=""),"направлено, но подтверждение направления не указано",IF($K93="","отметьте, идёт ли копия в пакет",IF($L93="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B93="","",IF(AND($E93&gt;0,LOWER($F93)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G93&lt;&gt;"",$I93=""),"направлено, но подтверждение направления не указано",IF($K93="","Отметьте включение копии в перечень приложений.",IF($L93="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="94">
@@ -3215,8 +3132,7 @@
         <v/>
       </c>
       <c r="M94" s="13">
-        <f>IF($B94="","",IF(AND($E94&gt;0,LOWER($F94)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G94&lt;&gt;"",$I94=""),"направлено, но подтверждение направления не указано",IF($K94="","отметьте, идёт ли копия в пакет",IF($L94="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B94="","",IF(AND($E94&gt;0,LOWER($F94)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G94&lt;&gt;"",$I94=""),"направлено, но подтверждение направления не указано",IF($K94="","Отметьте включение копии в перечень приложений.",IF($L94="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="95">
@@ -3239,8 +3155,7 @@
         <v/>
       </c>
       <c r="M95" s="13">
-        <f>IF($B95="","",IF(AND($E95&gt;0,LOWER($F95)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G95&lt;&gt;"",$I95=""),"направлено, но подтверждение направления не указано",IF($K95="","отметьте, идёт ли копия в пакет",IF($L95="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B95="","",IF(AND($E95&gt;0,LOWER($F95)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G95&lt;&gt;"",$I95=""),"направлено, но подтверждение направления не указано",IF($K95="","Отметьте включение копии в перечень приложений.",IF($L95="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="96">
@@ -3263,8 +3178,7 @@
         <v/>
       </c>
       <c r="M96" s="13">
-        <f>IF($B96="","",IF(AND($E96&gt;0,LOWER($F96)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G96&lt;&gt;"",$I96=""),"направлено, но подтверждение направления не указано",IF($K96="","отметьте, идёт ли копия в пакет",IF($L96="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B96="","",IF(AND($E96&gt;0,LOWER($F96)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G96&lt;&gt;"",$I96=""),"направлено, но подтверждение направления не указано",IF($K96="","Отметьте включение копии в перечень приложений.",IF($L96="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="97">
@@ -3287,8 +3201,7 @@
         <v/>
       </c>
       <c r="M97" s="13">
-        <f>IF($B97="","",IF(AND($E97&gt;0,LOWER($F97)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G97&lt;&gt;"",$I97=""),"направлено, но подтверждение направления не указано",IF($K97="","отметьте, идёт ли копия в пакет",IF($L97="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B97="","",IF(AND($E97&gt;0,LOWER($F97)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G97&lt;&gt;"",$I97=""),"направлено, но подтверждение направления не указано",IF($K97="","Отметьте включение копии в перечень приложений.",IF($L97="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="98">
@@ -3311,8 +3224,7 @@
         <v/>
       </c>
       <c r="M98" s="13">
-        <f>IF($B98="","",IF(AND($E98&gt;0,LOWER($F98)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G98&lt;&gt;"",$I98=""),"направлено, но подтверждение направления не указано",IF($K98="","отметьте, идёт ли копия в пакет",IF($L98="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B98="","",IF(AND($E98&gt;0,LOWER($F98)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G98&lt;&gt;"",$I98=""),"направлено, но подтверждение направления не указано",IF($K98="","Отметьте включение копии в перечень приложений.",IF($L98="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="99">
@@ -3335,8 +3247,7 @@
         <v/>
       </c>
       <c r="M99" s="13">
-        <f>IF($B99="","",IF(AND($E99&gt;0,LOWER($F99)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G99&lt;&gt;"",$I99=""),"направлено, но подтверждение направления не указано",IF($K99="","отметьте, идёт ли копия в пакет",IF($L99="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B99="","",IF(AND($E99&gt;0,LOWER($F99)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G99&lt;&gt;"",$I99=""),"направлено, но подтверждение направления не указано",IF($K99="","Отметьте включение копии в перечень приложений.",IF($L99="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="100">
@@ -3359,8 +3270,7 @@
         <v/>
       </c>
       <c r="M100" s="13">
-        <f>IF($B100="","",IF(AND($E100&gt;0,LOWER($F100)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G100&lt;&gt;"",$I100=""),"направлено, но подтверждение направления не указано",IF($K100="","отметьте, идёт ли копия в пакет",IF($L100="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B100="","",IF(AND($E100&gt;0,LOWER($F100)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G100&lt;&gt;"",$I100=""),"направлено, но подтверждение направления не указано",IF($K100="","Отметьте включение копии в перечень приложений.",IF($L100="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="101">
@@ -3383,8 +3293,7 @@
         <v/>
       </c>
       <c r="M101" s="13">
-        <f>IF($B101="","",IF(AND($E101&gt;0,LOWER($F101)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G101&lt;&gt;"",$I101=""),"направлено, но подтверждение направления не указано",IF($K101="","отметьте, идёт ли копия в пакет",IF($L101="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B101="","",IF(AND($E101&gt;0,LOWER($F101)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G101&lt;&gt;"",$I101=""),"направлено, но подтверждение направления не указано",IF($K101="","Отметьте включение копии в перечень приложений.",IF($L101="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="102">
@@ -3407,8 +3316,7 @@
         <v/>
       </c>
       <c r="M102" s="13">
-        <f>IF($B102="","",IF(AND($E102&gt;0,LOWER($F102)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G102&lt;&gt;"",$I102=""),"направлено, но подтверждение направления не указано",IF($K102="","отметьте, идёт ли копия в пакет",IF($L102="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B102="","",IF(AND($E102&gt;0,LOWER($F102)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G102&lt;&gt;"",$I102=""),"направлено, но подтверждение направления не указано",IF($K102="","Отметьте включение копии в перечень приложений.",IF($L102="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="103">
@@ -3431,8 +3339,7 @@
         <v/>
       </c>
       <c r="M103" s="13">
-        <f>IF($B103="","",IF(AND($E103&gt;0,LOWER($F103)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G103&lt;&gt;"",$I103=""),"направлено, но подтверждение направления не указано",IF($K103="","отметьте, идёт ли копия в пакет",IF($L103="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B103="","",IF(AND($E103&gt;0,LOWER($F103)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G103&lt;&gt;"",$I103=""),"направлено, но подтверждение направления не указано",IF($K103="","Отметьте включение копии в перечень приложений.",IF($L103="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="104">
@@ -3455,8 +3362,7 @@
         <v/>
       </c>
       <c r="M104" s="13">
-        <f>IF($B104="","",IF(AND($E104&gt;0,LOWER($F104)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G104&lt;&gt;"",$I104=""),"направлено, но подтверждение направления не указано",IF($K104="","отметьте, идёт ли копия в пакет",IF($L104="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B104="","",IF(AND($E104&gt;0,LOWER($F104)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G104&lt;&gt;"",$I104=""),"направлено, но подтверждение направления не указано",IF($K104="","Отметьте включение копии в перечень приложений.",IF($L104="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="105">
@@ -3479,8 +3385,7 @@
         <v/>
       </c>
       <c r="M105" s="13">
-        <f>IF($B105="","",IF(AND($E105&gt;0,LOWER($F105)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G105&lt;&gt;"",$I105=""),"направлено, но подтверждение направления не указано",IF($K105="","отметьте, идёт ли копия в пакет",IF($L105="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B105="","",IF(AND($E105&gt;0,LOWER($F105)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G105&lt;&gt;"",$I105=""),"направлено, но подтверждение направления не указано",IF($K105="","Отметьте включение копии в перечень приложений.",IF($L105="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="106">
@@ -3503,8 +3408,7 @@
         <v/>
       </c>
       <c r="M106" s="13">
-        <f>IF($B106="","",IF(AND($E106&gt;0,LOWER($F106)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G106&lt;&gt;"",$I106=""),"направлено, но подтверждение направления не указано",IF($K106="","отметьте, идёт ли копия в пакет",IF($L106="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B106="","",IF(AND($E106&gt;0,LOWER($F106)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G106&lt;&gt;"",$I106=""),"направлено, но подтверждение направления не указано",IF($K106="","Отметьте включение копии в перечень приложений.",IF($L106="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="107">
@@ -3527,8 +3431,7 @@
         <v/>
       </c>
       <c r="M107" s="13">
-        <f>IF($B107="","",IF(AND($E107&gt;0,LOWER($F107)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G107&lt;&gt;"",$I107=""),"направлено, но подтверждение направления не указано",IF($K107="","отметьте, идёт ли копия в пакет",IF($L107="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B107="","",IF(AND($E107&gt;0,LOWER($F107)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G107&lt;&gt;"",$I107=""),"направлено, но подтверждение направления не указано",IF($K107="","Отметьте включение копии в перечень приложений.",IF($L107="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="108">
@@ -3551,8 +3454,7 @@
         <v/>
       </c>
       <c r="M108" s="13">
-        <f>IF($B108="","",IF(AND($E108&gt;0,LOWER($F108)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G108&lt;&gt;"",$I108=""),"направлено, но подтверждение направления не указано",IF($K108="","отметьте, идёт ли копия в пакет",IF($L108="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B108="","",IF(AND($E108&gt;0,LOWER($F108)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G108&lt;&gt;"",$I108=""),"направлено, но подтверждение направления не указано",IF($K108="","Отметьте включение копии в перечень приложений.",IF($L108="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="109">
@@ -3575,8 +3477,7 @@
         <v/>
       </c>
       <c r="M109" s="13">
-        <f>IF($B109="","",IF(AND($E109&gt;0,LOWER($F109)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G109&lt;&gt;"",$I109=""),"направлено, но подтверждение направления не указано",IF($K109="","отметьте, идёт ли копия в пакет",IF($L109="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B109="","",IF(AND($E109&gt;0,LOWER($F109)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G109&lt;&gt;"",$I109=""),"направлено, но подтверждение направления не указано",IF($K109="","Отметьте включение копии в перечень приложений.",IF($L109="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="110">
@@ -3599,8 +3500,7 @@
         <v/>
       </c>
       <c r="M110" s="13">
-        <f>IF($B110="","",IF(AND($E110&gt;0,LOWER($F110)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G110&lt;&gt;"",$I110=""),"направлено, но подтверждение направления не указано",IF($K110="","отметьте, идёт ли копия в пакет",IF($L110="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B110="","",IF(AND($E110&gt;0,LOWER($F110)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G110&lt;&gt;"",$I110=""),"направлено, но подтверждение направления не указано",IF($K110="","Отметьте включение копии в перечень приложений.",IF($L110="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="111">
@@ -3623,8 +3523,7 @@
         <v/>
       </c>
       <c r="M111" s="13">
-        <f>IF($B111="","",IF(AND($E111&gt;0,LOWER($F111)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G111&lt;&gt;"",$I111=""),"направлено, но подтверждение направления не указано",IF($K111="","отметьте, идёт ли копия в пакет",IF($L111="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B111="","",IF(AND($E111&gt;0,LOWER($F111)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G111&lt;&gt;"",$I111=""),"направлено, но подтверждение направления не указано",IF($K111="","Отметьте включение копии в перечень приложений.",IF($L111="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="112">
@@ -3647,8 +3546,7 @@
         <v/>
       </c>
       <c r="M112" s="13">
-        <f>IF($B112="","",IF(AND($E112&gt;0,LOWER($F112)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G112&lt;&gt;"",$I112=""),"направлено, но подтверждение направления не указано",IF($K112="","отметьте, идёт ли копия в пакет",IF($L112="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B112="","",IF(AND($E112&gt;0,LOWER($F112)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G112&lt;&gt;"",$I112=""),"направлено, но подтверждение направления не указано",IF($K112="","Отметьте включение копии в перечень приложений.",IF($L112="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="113">
@@ -3671,8 +3569,7 @@
         <v/>
       </c>
       <c r="M113" s="13">
-        <f>IF($B113="","",IF(AND($E113&gt;0,LOWER($F113)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G113&lt;&gt;"",$I113=""),"направлено, но подтверждение направления не указано",IF($K113="","отметьте, идёт ли копия в пакет",IF($L113="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B113="","",IF(AND($E113&gt;0,LOWER($F113)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G113&lt;&gt;"",$I113=""),"направлено, но подтверждение направления не указано",IF($K113="","Отметьте включение копии в перечень приложений.",IF($L113="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="114">
@@ -3695,8 +3592,7 @@
         <v/>
       </c>
       <c r="M114" s="13">
-        <f>IF($B114="","",IF(AND($E114&gt;0,LOWER($F114)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G114&lt;&gt;"",$I114=""),"направлено, но подтверждение направления не указано",IF($K114="","отметьте, идёт ли копия в пакет",IF($L114="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B114="","",IF(AND($E114&gt;0,LOWER($F114)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G114&lt;&gt;"",$I114=""),"направлено, но подтверждение направления не указано",IF($K114="","Отметьте включение копии в перечень приложений.",IF($L114="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="115">
@@ -3719,8 +3615,7 @@
         <v/>
       </c>
       <c r="M115" s="13">
-        <f>IF($B115="","",IF(AND($E115&gt;0,LOWER($F115)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G115&lt;&gt;"",$I115=""),"направлено, но подтверждение направления не указано",IF($K115="","отметьте, идёт ли копия в пакет",IF($L115="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B115="","",IF(AND($E115&gt;0,LOWER($F115)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G115&lt;&gt;"",$I115=""),"направлено, но подтверждение направления не указано",IF($K115="","Отметьте включение копии в перечень приложений.",IF($L115="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="116">
@@ -3743,8 +3638,7 @@
         <v/>
       </c>
       <c r="M116" s="13">
-        <f>IF($B116="","",IF(AND($E116&gt;0,LOWER($F116)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G116&lt;&gt;"",$I116=""),"направлено, но подтверждение направления не указано",IF($K116="","отметьте, идёт ли копия в пакет",IF($L116="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B116="","",IF(AND($E116&gt;0,LOWER($F116)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G116&lt;&gt;"",$I116=""),"направлено, но подтверждение направления не указано",IF($K116="","Отметьте включение копии в перечень приложений.",IF($L116="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="117">
@@ -3767,8 +3661,7 @@
         <v/>
       </c>
       <c r="M117" s="13">
-        <f>IF($B117="","",IF(AND($E117&gt;0,LOWER($F117)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G117&lt;&gt;"",$I117=""),"направлено, но подтверждение направления не указано",IF($K117="","отметьте, идёт ли копия в пакет",IF($L117="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B117="","",IF(AND($E117&gt;0,LOWER($F117)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G117&lt;&gt;"",$I117=""),"направлено, но подтверждение направления не указано",IF($K117="","Отметьте включение копии в перечень приложений.",IF($L117="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="118">
@@ -3791,8 +3684,7 @@
         <v/>
       </c>
       <c r="M118" s="13">
-        <f>IF($B118="","",IF(AND($E118&gt;0,LOWER($F118)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G118&lt;&gt;"",$I118=""),"направлено, но подтверждение направления не указано",IF($K118="","отметьте, идёт ли копия в пакет",IF($L118="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B118="","",IF(AND($E118&gt;0,LOWER($F118)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G118&lt;&gt;"",$I118=""),"направлено, но подтверждение направления не указано",IF($K118="","Отметьте включение копии в перечень приложений.",IF($L118="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="119">
@@ -3815,8 +3707,7 @@
         <v/>
       </c>
       <c r="M119" s="13">
-        <f>IF($B119="","",IF(AND($E119&gt;0,LOWER($F119)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G119&lt;&gt;"",$I119=""),"направлено, но подтверждение направления не указано",IF($K119="","отметьте, идёт ли копия в пакет",IF($L119="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B119="","",IF(AND($E119&gt;0,LOWER($F119)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G119&lt;&gt;"",$I119=""),"направлено, но подтверждение направления не указано",IF($K119="","Отметьте включение копии в перечень приложений.",IF($L119="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="120">
@@ -3839,8 +3730,7 @@
         <v/>
       </c>
       <c r="M120" s="13">
-        <f>IF($B120="","",IF(AND($E120&gt;0,LOWER($F120)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G120&lt;&gt;"",$I120=""),"направлено, но подтверждение направления не указано",IF($K120="","отметьте, идёт ли копия в пакет",IF($L120="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B120="","",IF(AND($E120&gt;0,LOWER($F120)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G120&lt;&gt;"",$I120=""),"направлено, но подтверждение направления не указано",IF($K120="","Отметьте включение копии в перечень приложений.",IF($L120="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="121">
@@ -3863,8 +3753,7 @@
         <v/>
       </c>
       <c r="M121" s="13">
-        <f>IF($B121="","",IF(AND($E121&gt;0,LOWER($F121)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G121&lt;&gt;"",$I121=""),"направлено, но подтверждение направления не указано",IF($K121="","отметьте, идёт ли копия в пакет",IF($L121="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B121="","",IF(AND($E121&gt;0,LOWER($F121)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G121&lt;&gt;"",$I121=""),"направлено, но подтверждение направления не указано",IF($K121="","Отметьте включение копии в перечень приложений.",IF($L121="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="122">
@@ -3887,8 +3776,7 @@
         <v/>
       </c>
       <c r="M122" s="13">
-        <f>IF($B122="","",IF(AND($E122&gt;0,LOWER($F122)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G122&lt;&gt;"",$I122=""),"направлено, но подтверждение направления не указано",IF($K122="","отметьте, идёт ли копия в пакет",IF($L122="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B122="","",IF(AND($E122&gt;0,LOWER($F122)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G122&lt;&gt;"",$I122=""),"направлено, но подтверждение направления не указано",IF($K122="","Отметьте включение копии в перечень приложений.",IF($L122="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="123">
@@ -3911,8 +3799,7 @@
         <v/>
       </c>
       <c r="M123" s="13">
-        <f>IF($B123="","",IF(AND($E123&gt;0,LOWER($F123)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G123&lt;&gt;"",$I123=""),"направлено, но подтверждение направления не указано",IF($K123="","отметьте, идёт ли копия в пакет",IF($L123="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B123="","",IF(AND($E123&gt;0,LOWER($F123)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G123&lt;&gt;"",$I123=""),"направлено, но подтверждение направления не указано",IF($K123="","Отметьте включение копии в перечень приложений.",IF($L123="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="124">
@@ -3935,8 +3822,7 @@
         <v/>
       </c>
       <c r="M124" s="13">
-        <f>IF($B124="","",IF(AND($E124&gt;0,LOWER($F124)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G124&lt;&gt;"",$I124=""),"направлено, но подтверждение направления не указано",IF($K124="","отметьте, идёт ли копия в пакет",IF($L124="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B124="","",IF(AND($E124&gt;0,LOWER($F124)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G124&lt;&gt;"",$I124=""),"направлено, но подтверждение направления не указано",IF($K124="","Отметьте включение копии в перечень приложений.",IF($L124="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="125">
@@ -3959,8 +3845,7 @@
         <v/>
       </c>
       <c r="M125" s="13">
-        <f>IF($B125="","",IF(AND($E125&gt;0,LOWER($F125)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G125&lt;&gt;"",$I125=""),"направлено, но подтверждение направления не указано",IF($K125="","отметьте, идёт ли копия в пакет",IF($L125="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B125="","",IF(AND($E125&gt;0,LOWER($F125)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G125&lt;&gt;"",$I125=""),"направлено, но подтверждение направления не указано",IF($K125="","Отметьте включение копии в перечень приложений.",IF($L125="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="126">
@@ -3983,8 +3868,7 @@
         <v/>
       </c>
       <c r="M126" s="13">
-        <f>IF($B126="","",IF(AND($E126&gt;0,LOWER($F126)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G126&lt;&gt;"",$I126=""),"направлено, но подтверждение направления не указано",IF($K126="","отметьте, идёт ли копия в пакет",IF($L126="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B126="","",IF(AND($E126&gt;0,LOWER($F126)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G126&lt;&gt;"",$I126=""),"направлено, но подтверждение направления не указано",IF($K126="","Отметьте включение копии в перечень приложений.",IF($L126="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="127">
@@ -4007,8 +3891,7 @@
         <v/>
       </c>
       <c r="M127" s="13">
-        <f>IF($B127="","",IF(AND($E127&gt;0,LOWER($F127)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G127&lt;&gt;"",$I127=""),"направлено, но подтверждение направления не указано",IF($K127="","отметьте, идёт ли копия в пакет",IF($L127="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B127="","",IF(AND($E127&gt;0,LOWER($F127)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G127&lt;&gt;"",$I127=""),"направлено, но подтверждение направления не указано",IF($K127="","Отметьте включение копии в перечень приложений.",IF($L127="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="128">
@@ -4031,8 +3914,7 @@
         <v/>
       </c>
       <c r="M128" s="13">
-        <f>IF($B128="","",IF(AND($E128&gt;0,LOWER($F128)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G128&lt;&gt;"",$I128=""),"направлено, но подтверждение направления не указано",IF($K128="","отметьте, идёт ли копия в пакет",IF($L128="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B128="","",IF(AND($E128&gt;0,LOWER($F128)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G128&lt;&gt;"",$I128=""),"направлено, но подтверждение направления не указано",IF($K128="","Отметьте включение копии в перечень приложений.",IF($L128="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="129">
@@ -4055,8 +3937,7 @@
         <v/>
       </c>
       <c r="M129" s="13">
-        <f>IF($B129="","",IF(AND($E129&gt;0,LOWER($F129)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G129&lt;&gt;"",$I129=""),"направлено, но подтверждение направления не указано",IF($K129="","отметьте, идёт ли копия в пакет",IF($L129="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B129="","",IF(AND($E129&gt;0,LOWER($F129)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G129&lt;&gt;"",$I129=""),"направлено, но подтверждение направления не указано",IF($K129="","Отметьте включение копии в перечень приложений.",IF($L129="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="130">
@@ -4079,8 +3960,7 @@
         <v/>
       </c>
       <c r="M130" s="13">
-        <f>IF($B130="","",IF(AND($E130&gt;0,LOWER($F130)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G130&lt;&gt;"",$I130=""),"направлено, но подтверждение направления не указано",IF($K130="","отметьте, идёт ли копия в пакет",IF($L130="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B130="","",IF(AND($E130&gt;0,LOWER($F130)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G130&lt;&gt;"",$I130=""),"направлено, но подтверждение направления не указано",IF($K130="","Отметьте включение копии в перечень приложений.",IF($L130="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="131">
@@ -4103,8 +3983,7 @@
         <v/>
       </c>
       <c r="M131" s="13">
-        <f>IF($B131="","",IF(AND($E131&gt;0,LOWER($F131)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G131&lt;&gt;"",$I131=""),"направлено, но подтверждение направления не указано",IF($K131="","отметьте, идёт ли копия в пакет",IF($L131="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B131="","",IF(AND($E131&gt;0,LOWER($F131)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G131&lt;&gt;"",$I131=""),"направлено, но подтверждение направления не указано",IF($K131="","Отметьте включение копии в перечень приложений.",IF($L131="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="132">
@@ -4127,8 +4006,7 @@
         <v/>
       </c>
       <c r="M132" s="13">
-        <f>IF($B132="","",IF(AND($E132&gt;0,LOWER($F132)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G132&lt;&gt;"",$I132=""),"направлено, но подтверждение направления не указано",IF($K132="","отметьте, идёт ли копия в пакет",IF($L132="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B132="","",IF(AND($E132&gt;0,LOWER($F132)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G132&lt;&gt;"",$I132=""),"направлено, но подтверждение направления не указано",IF($K132="","Отметьте включение копии в перечень приложений.",IF($L132="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="133">
@@ -4151,8 +4029,7 @@
         <v/>
       </c>
       <c r="M133" s="13">
-        <f>IF($B133="","",IF(AND($E133&gt;0,LOWER($F133)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G133&lt;&gt;"",$I133=""),"направлено, но подтверждение направления не указано",IF($K133="","отметьте, идёт ли копия в пакет",IF($L133="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B133="","",IF(AND($E133&gt;0,LOWER($F133)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G133&lt;&gt;"",$I133=""),"направлено, но подтверждение направления не указано",IF($K133="","Отметьте включение копии в перечень приложений.",IF($L133="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="134">
@@ -4175,8 +4052,7 @@
         <v/>
       </c>
       <c r="M134" s="13">
-        <f>IF($B134="","",IF(AND($E134&gt;0,LOWER($F134)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G134&lt;&gt;"",$I134=""),"направлено, но подтверждение направления не указано",IF($K134="","отметьте, идёт ли копия в пакет",IF($L134="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B134="","",IF(AND($E134&gt;0,LOWER($F134)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G134&lt;&gt;"",$I134=""),"направлено, но подтверждение направления не указано",IF($K134="","Отметьте включение копии в перечень приложений.",IF($L134="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="135">
@@ -4199,8 +4075,7 @@
         <v/>
       </c>
       <c r="M135" s="13">
-        <f>IF($B135="","",IF(AND($E135&gt;0,LOWER($F135)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G135&lt;&gt;"",$I135=""),"направлено, но подтверждение направления не указано",IF($K135="","отметьте, идёт ли копия в пакет",IF($L135="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B135="","",IF(AND($E135&gt;0,LOWER($F135)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G135&lt;&gt;"",$I135=""),"направлено, но подтверждение направления не указано",IF($K135="","Отметьте включение копии в перечень приложений.",IF($L135="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="136">
@@ -4223,8 +4098,7 @@
         <v/>
       </c>
       <c r="M136" s="13">
-        <f>IF($B136="","",IF(AND($E136&gt;0,LOWER($F136)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G136&lt;&gt;"",$I136=""),"направлено, но подтверждение направления не указано",IF($K136="","отметьте, идёт ли копия в пакет",IF($L136="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B136="","",IF(AND($E136&gt;0,LOWER($F136)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G136&lt;&gt;"",$I136=""),"направлено, но подтверждение направления не указано",IF($K136="","Отметьте включение копии в перечень приложений.",IF($L136="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="137">
@@ -4247,8 +4121,7 @@
         <v/>
       </c>
       <c r="M137" s="13">
-        <f>IF($B137="","",IF(AND($E137&gt;0,LOWER($F137)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G137&lt;&gt;"",$I137=""),"направлено, но подтверждение направления не указано",IF($K137="","отметьте, идёт ли копия в пакет",IF($L137="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B137="","",IF(AND($E137&gt;0,LOWER($F137)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G137&lt;&gt;"",$I137=""),"направлено, но подтверждение направления не указано",IF($K137="","Отметьте включение копии в перечень приложений.",IF($L137="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="138">
@@ -4271,8 +4144,7 @@
         <v/>
       </c>
       <c r="M138" s="13">
-        <f>IF($B138="","",IF(AND($E138&gt;0,LOWER($F138)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G138&lt;&gt;"",$I138=""),"направлено, но подтверждение направления не указано",IF($K138="","отметьте, идёт ли копия в пакет",IF($L138="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B138="","",IF(AND($E138&gt;0,LOWER($F138)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G138&lt;&gt;"",$I138=""),"направлено, но подтверждение направления не указано",IF($K138="","Отметьте включение копии в перечень приложений.",IF($L138="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="139">
@@ -4295,8 +4167,7 @@
         <v/>
       </c>
       <c r="M139" s="13">
-        <f>IF($B139="","",IF(AND($E139&gt;0,LOWER($F139)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G139&lt;&gt;"",$I139=""),"направлено, но подтверждение направления не указано",IF($K139="","отметьте, идёт ли копия в пакет",IF($L139="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B139="","",IF(AND($E139&gt;0,LOWER($F139)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G139&lt;&gt;"",$I139=""),"направлено, но подтверждение направления не указано",IF($K139="","Отметьте включение копии в перечень приложений.",IF($L139="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="140">
@@ -4319,8 +4190,7 @@
         <v/>
       </c>
       <c r="M140" s="13">
-        <f>IF($B140="","",IF(AND($E140&gt;0,LOWER($F140)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G140&lt;&gt;"",$I140=""),"направлено, но подтверждение направления не указано",IF($K140="","отметьте, идёт ли копия в пакет",IF($L140="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B140="","",IF(AND($E140&gt;0,LOWER($F140)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G140&lt;&gt;"",$I140=""),"направлено, но подтверждение направления не указано",IF($K140="","Отметьте включение копии в перечень приложений.",IF($L140="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="141">
@@ -4343,8 +4213,7 @@
         <v/>
       </c>
       <c r="M141" s="13">
-        <f>IF($B141="","",IF(AND($E141&gt;0,LOWER($F141)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G141&lt;&gt;"",$I141=""),"направлено, но подтверждение направления не указано",IF($K141="","отметьте, идёт ли копия в пакет",IF($L141="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B141="","",IF(AND($E141&gt;0,LOWER($F141)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G141&lt;&gt;"",$I141=""),"направлено, но подтверждение направления не указано",IF($K141="","Отметьте включение копии в перечень приложений.",IF($L141="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="142">
@@ -4367,8 +4236,7 @@
         <v/>
       </c>
       <c r="M142" s="13">
-        <f>IF($B142="","",IF(AND($E142&gt;0,LOWER($F142)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G142&lt;&gt;"",$I142=""),"направлено, но подтверждение направления не указано",IF($K142="","отметьте, идёт ли копия в пакет",IF($L142="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B142="","",IF(AND($E142&gt;0,LOWER($F142)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G142&lt;&gt;"",$I142=""),"направлено, но подтверждение направления не указано",IF($K142="","Отметьте включение копии в перечень приложений.",IF($L142="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="143">
@@ -4391,8 +4259,7 @@
         <v/>
       </c>
       <c r="M143" s="13">
-        <f>IF($B143="","",IF(AND($E143&gt;0,LOWER($F143)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G143&lt;&gt;"",$I143=""),"направлено, но подтверждение направления не указано",IF($K143="","отметьте, идёт ли копия в пакет",IF($L143="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B143="","",IF(AND($E143&gt;0,LOWER($F143)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G143&lt;&gt;"",$I143=""),"направлено, но подтверждение направления не указано",IF($K143="","Отметьте включение копии в перечень приложений.",IF($L143="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="144">
@@ -4415,8 +4282,7 @@
         <v/>
       </c>
       <c r="M144" s="13">
-        <f>IF($B144="","",IF(AND($E144&gt;0,LOWER($F144)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G144&lt;&gt;"",$I144=""),"направлено, но подтверждение направления не указано",IF($K144="","отметьте, идёт ли копия в пакет",IF($L144="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B144="","",IF(AND($E144&gt;0,LOWER($F144)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G144&lt;&gt;"",$I144=""),"направлено, но подтверждение направления не указано",IF($K144="","Отметьте включение копии в перечень приложений.",IF($L144="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="145">
@@ -4439,8 +4305,7 @@
         <v/>
       </c>
       <c r="M145" s="13">
-        <f>IF($B145="","",IF(AND($E145&gt;0,LOWER($F145)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G145&lt;&gt;"",$I145=""),"направлено, но подтверждение направления не указано",IF($K145="","отметьте, идёт ли копия в пакет",IF($L145="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B145="","",IF(AND($E145&gt;0,LOWER($F145)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G145&lt;&gt;"",$I145=""),"направлено, но подтверждение направления не указано",IF($K145="","Отметьте включение копии в перечень приложений.",IF($L145="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="146">
@@ -4463,8 +4328,7 @@
         <v/>
       </c>
       <c r="M146" s="13">
-        <f>IF($B146="","",IF(AND($E146&gt;0,LOWER($F146)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G146&lt;&gt;"",$I146=""),"направлено, но подтверждение направления не указано",IF($K146="","отметьте, идёт ли копия в пакет",IF($L146="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B146="","",IF(AND($E146&gt;0,LOWER($F146)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G146&lt;&gt;"",$I146=""),"направлено, но подтверждение направления не указано",IF($K146="","Отметьте включение копии в перечень приложений.",IF($L146="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="147">
@@ -4487,8 +4351,7 @@
         <v/>
       </c>
       <c r="M147" s="13">
-        <f>IF($B147="","",IF(AND($E147&gt;0,LOWER($F147)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G147&lt;&gt;"",$I147=""),"направлено, но подтверждение направления не указано",IF($K147="","отметьте, идёт ли копия в пакет",IF($L147="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B147="","",IF(AND($E147&gt;0,LOWER($F147)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G147&lt;&gt;"",$I147=""),"направлено, но подтверждение направления не указано",IF($K147="","Отметьте включение копии в перечень приложений.",IF($L147="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="148">
@@ -4511,8 +4374,7 @@
         <v/>
       </c>
       <c r="M148" s="13">
-        <f>IF($B148="","",IF(AND($E148&gt;0,LOWER($F148)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G148&lt;&gt;"",$I148=""),"направлено, но подтверждение направления не указано",IF($K148="","отметьте, идёт ли копия в пакет",IF($L148="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B148="","",IF(AND($E148&gt;0,LOWER($F148)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G148&lt;&gt;"",$I148=""),"направлено, но подтверждение направления не указано",IF($K148="","Отметьте включение копии в перечень приложений.",IF($L148="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="149">
@@ -4535,8 +4397,7 @@
         <v/>
       </c>
       <c r="M149" s="13">
-        <f>IF($B149="","",IF(AND($E149&gt;0,LOWER($F149)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G149&lt;&gt;"",$I149=""),"направлено, но подтверждение направления не указано",IF($K149="","отметьте, идёт ли копия в пакет",IF($L149="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B149="","",IF(AND($E149&gt;0,LOWER($F149)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G149&lt;&gt;"",$I149=""),"направлено, но подтверждение направления не указано",IF($K149="","Отметьте включение копии в перечень приложений.",IF($L149="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="150">
@@ -4559,8 +4420,7 @@
         <v/>
       </c>
       <c r="M150" s="13">
-        <f>IF($B150="","",IF(AND($E150&gt;0,LOWER($F150)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G150&lt;&gt;"",$I150=""),"направлено, но подтверждение направления не указано",IF($K150="","отметьте, идёт ли копия в пакет",IF($L150="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B150="","",IF(AND($E150&gt;0,LOWER($F150)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G150&lt;&gt;"",$I150=""),"направлено, но подтверждение направления не указано",IF($K150="","Отметьте включение копии в перечень приложений.",IF($L150="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="151">
@@ -4583,8 +4443,7 @@
         <v/>
       </c>
       <c r="M151" s="13">
-        <f>IF($B151="","",IF(AND($E151&gt;0,LOWER($F151)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G151&lt;&gt;"",$I151=""),"направлено, но подтверждение направления не указано",IF($K151="","отметьте, идёт ли копия в пакет",IF($L151="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B151="","",IF(AND($E151&gt;0,LOWER($F151)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G151&lt;&gt;"",$I151=""),"направлено, но подтверждение направления не указано",IF($K151="","Отметьте включение копии в перечень приложений.",IF($L151="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="152">
@@ -4607,8 +4466,7 @@
         <v/>
       </c>
       <c r="M152" s="13">
-        <f>IF($B152="","",IF(AND($E152&gt;0,LOWER($F152)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G152&lt;&gt;"",$I152=""),"направлено, но подтверждение направления не указано",IF($K152="","отметьте, идёт ли копия в пакет",IF($L152="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B152="","",IF(AND($E152&gt;0,LOWER($F152)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G152&lt;&gt;"",$I152=""),"направлено, но подтверждение направления не указано",IF($K152="","Отметьте включение копии в перечень приложений.",IF($L152="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="153">
@@ -4631,8 +4489,7 @@
         <v/>
       </c>
       <c r="M153" s="13">
-        <f>IF($B153="","",IF(AND($E153&gt;0,LOWER($F153)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G153&lt;&gt;"",$I153=""),"направлено, но подтверждение направления не указано",IF($K153="","отметьте, идёт ли копия в пакет",IF($L153="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B153="","",IF(AND($E153&gt;0,LOWER($F153)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G153&lt;&gt;"",$I153=""),"направлено, но подтверждение направления не указано",IF($K153="","Отметьте включение копии в перечень приложений.",IF($L153="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="154">
@@ -4655,8 +4512,7 @@
         <v/>
       </c>
       <c r="M154" s="13">
-        <f>IF($B154="","",IF(AND($E154&gt;0,LOWER($F154)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G154&lt;&gt;"",$I154=""),"направлено, но подтверждение направления не указано",IF($K154="","отметьте, идёт ли копия в пакет",IF($L154="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B154="","",IF(AND($E154&gt;0,LOWER($F154)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G154&lt;&gt;"",$I154=""),"направлено, но подтверждение направления не указано",IF($K154="","Отметьте включение копии в перечень приложений.",IF($L154="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="155">
@@ -4679,8 +4535,7 @@
         <v/>
       </c>
       <c r="M155" s="13">
-        <f>IF($B155="","",IF(AND($E155&gt;0,LOWER($F155)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G155&lt;&gt;"",$I155=""),"направлено, но подтверждение направления не указано",IF($K155="","отметьте, идёт ли копия в пакет",IF($L155="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B155="","",IF(AND($E155&gt;0,LOWER($F155)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G155&lt;&gt;"",$I155=""),"направлено, но подтверждение направления не указано",IF($K155="","Отметьте включение копии в перечень приложений.",IF($L155="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="156">
@@ -4703,8 +4558,7 @@
         <v/>
       </c>
       <c r="M156" s="13">
-        <f>IF($B156="","",IF(AND($E156&gt;0,LOWER($F156)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G156&lt;&gt;"",$I156=""),"направлено, но подтверждение направления не указано",IF($K156="","отметьте, идёт ли копия в пакет",IF($L156="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B156="","",IF(AND($E156&gt;0,LOWER($F156)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G156&lt;&gt;"",$I156=""),"направлено, но подтверждение направления не указано",IF($K156="","Отметьте включение копии в перечень приложений.",IF($L156="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="157">
@@ -4727,8 +4581,7 @@
         <v/>
       </c>
       <c r="M157" s="13">
-        <f>IF($B157="","",IF(AND($E157&gt;0,LOWER($F157)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G157&lt;&gt;"",$I157=""),"направлено, но подтверждение направления не указано",IF($K157="","отметьте, идёт ли копия в пакет",IF($L157="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B157="","",IF(AND($E157&gt;0,LOWER($F157)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G157&lt;&gt;"",$I157=""),"направлено, но подтверждение направления не указано",IF($K157="","Отметьте включение копии в перечень приложений.",IF($L157="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="158">
@@ -4751,8 +4604,7 @@
         <v/>
       </c>
       <c r="M158" s="13">
-        <f>IF($B158="","",IF(AND($E158&gt;0,LOWER($F158)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G158&lt;&gt;"",$I158=""),"направлено, но подтверждение направления не указано",IF($K158="","отметьте, идёт ли копия в пакет",IF($L158="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B158="","",IF(AND($E158&gt;0,LOWER($F158)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G158&lt;&gt;"",$I158=""),"направлено, но подтверждение направления не указано",IF($K158="","Отметьте включение копии в перечень приложений.",IF($L158="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="159">
@@ -4775,8 +4627,7 @@
         <v/>
       </c>
       <c r="M159" s="13">
-        <f>IF($B159="","",IF(AND($E159&gt;0,LOWER($F159)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G159&lt;&gt;"",$I159=""),"направлено, но подтверждение направления не указано",IF($K159="","отметьте, идёт ли копия в пакет",IF($L159="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B159="","",IF(AND($E159&gt;0,LOWER($F159)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G159&lt;&gt;"",$I159=""),"направлено, но подтверждение направления не указано",IF($K159="","Отметьте включение копии в перечень приложений.",IF($L159="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="160">
@@ -4799,8 +4650,7 @@
         <v/>
       </c>
       <c r="M160" s="13">
-        <f>IF($B160="","",IF(AND($E160&gt;0,LOWER($F160)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G160&lt;&gt;"",$I160=""),"направлено, но подтверждение направления не указано",IF($K160="","отметьте, идёт ли копия в пакет",IF($L160="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B160="","",IF(AND($E160&gt;0,LOWER($F160)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G160&lt;&gt;"",$I160=""),"направлено, но подтверждение направления не указано",IF($K160="","Отметьте включение копии в перечень приложений.",IF($L160="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="161">
@@ -4823,8 +4673,7 @@
         <v/>
       </c>
       <c r="M161" s="13">
-        <f>IF($B161="","",IF(AND($E161&gt;0,LOWER($F161)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G161&lt;&gt;"",$I161=""),"направлено, но подтверждение направления не указано",IF($K161="","отметьте, идёт ли копия в пакет",IF($L161="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B161="","",IF(AND($E161&gt;0,LOWER($F161)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G161&lt;&gt;"",$I161=""),"направлено, но подтверждение направления не указано",IF($K161="","Отметьте включение копии в перечень приложений.",IF($L161="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="162">
@@ -4847,8 +4696,7 @@
         <v/>
       </c>
       <c r="M162" s="13">
-        <f>IF($B162="","",IF(AND($E162&gt;0,LOWER($F162)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G162&lt;&gt;"",$I162=""),"направлено, но подтверждение направления не указано",IF($K162="","отметьте, идёт ли копия в пакет",IF($L162="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B162="","",IF(AND($E162&gt;0,LOWER($F162)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G162&lt;&gt;"",$I162=""),"направлено, но подтверждение направления не указано",IF($K162="","Отметьте включение копии в перечень приложений.",IF($L162="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="163">
@@ -4871,8 +4719,7 @@
         <v/>
       </c>
       <c r="M163" s="13">
-        <f>IF($B163="","",IF(AND($E163&gt;0,LOWER($F163)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G163&lt;&gt;"",$I163=""),"направлено, но подтверждение направления не указано",IF($K163="","отметьте, идёт ли копия в пакет",IF($L163="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B163="","",IF(AND($E163&gt;0,LOWER($F163)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G163&lt;&gt;"",$I163=""),"направлено, но подтверждение направления не указано",IF($K163="","Отметьте включение копии в перечень приложений.",IF($L163="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="164">
@@ -4895,8 +4742,7 @@
         <v/>
       </c>
       <c r="M164" s="13">
-        <f>IF($B164="","",IF(AND($E164&gt;0,LOWER($F164)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G164&lt;&gt;"",$I164=""),"направлено, но подтверждение направления не указано",IF($K164="","отметьте, идёт ли копия в пакет",IF($L164="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B164="","",IF(AND($E164&gt;0,LOWER($F164)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G164&lt;&gt;"",$I164=""),"направлено, но подтверждение направления не указано",IF($K164="","Отметьте включение копии в перечень приложений.",IF($L164="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="165">
@@ -4919,8 +4765,7 @@
         <v/>
       </c>
       <c r="M165" s="13">
-        <f>IF($B165="","",IF(AND($E165&gt;0,LOWER($F165)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G165&lt;&gt;"",$I165=""),"направлено, но подтверждение направления не указано",IF($K165="","отметьте, идёт ли копия в пакет",IF($L165="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B165="","",IF(AND($E165&gt;0,LOWER($F165)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G165&lt;&gt;"",$I165=""),"направлено, но подтверждение направления не указано",IF($K165="","Отметьте включение копии в перечень приложений.",IF($L165="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="166">
@@ -4943,8 +4788,7 @@
         <v/>
       </c>
       <c r="M166" s="13">
-        <f>IF($B166="","",IF(AND($E166&gt;0,LOWER($F166)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G166&lt;&gt;"",$I166=""),"направлено, но подтверждение направления не указано",IF($K166="","отметьте, идёт ли копия в пакет",IF($L166="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B166="","",IF(AND($E166&gt;0,LOWER($F166)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G166&lt;&gt;"",$I166=""),"направлено, но подтверждение направления не указано",IF($K166="","Отметьте включение копии в перечень приложений.",IF($L166="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="167">
@@ -4967,8 +4811,7 @@
         <v/>
       </c>
       <c r="M167" s="13">
-        <f>IF($B167="","",IF(AND($E167&gt;0,LOWER($F167)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G167&lt;&gt;"",$I167=""),"направлено, но подтверждение направления не указано",IF($K167="","отметьте, идёт ли копия в пакет",IF($L167="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B167="","",IF(AND($E167&gt;0,LOWER($F167)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G167&lt;&gt;"",$I167=""),"направлено, но подтверждение направления не указано",IF($K167="","Отметьте включение копии в перечень приложений.",IF($L167="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="168">
@@ -4991,8 +4834,7 @@
         <v/>
       </c>
       <c r="M168" s="13">
-        <f>IF($B168="","",IF(AND($E168&gt;0,LOWER($F168)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G168&lt;&gt;"",$I168=""),"направлено, но подтверждение направления не указано",IF($K168="","отметьте, идёт ли копия в пакет",IF($L168="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B168="","",IF(AND($E168&gt;0,LOWER($F168)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G168&lt;&gt;"",$I168=""),"направлено, но подтверждение направления не указано",IF($K168="","Отметьте включение копии в перечень приложений.",IF($L168="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="169">
@@ -5015,8 +4857,7 @@
         <v/>
       </c>
       <c r="M169" s="13">
-        <f>IF($B169="","",IF(AND($E169&gt;0,LOWER($F169)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G169&lt;&gt;"",$I169=""),"направлено, но подтверждение направления не указано",IF($K169="","отметьте, идёт ли копия в пакет",IF($L169="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B169="","",IF(AND($E169&gt;0,LOWER($F169)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G169&lt;&gt;"",$I169=""),"направлено, но подтверждение направления не указано",IF($K169="","Отметьте включение копии в перечень приложений.",IF($L169="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="170">
@@ -5039,8 +4880,7 @@
         <v/>
       </c>
       <c r="M170" s="13">
-        <f>IF($B170="","",IF(AND($E170&gt;0,LOWER($F170)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G170&lt;&gt;"",$I170=""),"направлено, но подтверждение направления не указано",IF($K170="","отметьте, идёт ли копия в пакет",IF($L170="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B170="","",IF(AND($E170&gt;0,LOWER($F170)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G170&lt;&gt;"",$I170=""),"направлено, но подтверждение направления не указано",IF($K170="","Отметьте включение копии в перечень приложений.",IF($L170="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="171">
@@ -5063,8 +4903,7 @@
         <v/>
       </c>
       <c r="M171" s="13">
-        <f>IF($B171="","",IF(AND($E171&gt;0,LOWER($F171)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G171&lt;&gt;"",$I171=""),"направлено, но подтверждение направления не указано",IF($K171="","отметьте, идёт ли копия в пакет",IF($L171="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B171="","",IF(AND($E171&gt;0,LOWER($F171)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G171&lt;&gt;"",$I171=""),"направлено, но подтверждение направления не указано",IF($K171="","Отметьте включение копии в перечень приложений.",IF($L171="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="172">
@@ -5087,8 +4926,7 @@
         <v/>
       </c>
       <c r="M172" s="13">
-        <f>IF($B172="","",IF(AND($E172&gt;0,LOWER($F172)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G172&lt;&gt;"",$I172=""),"направлено, но подтверждение направления не указано",IF($K172="","отметьте, идёт ли копия в пакет",IF($L172="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B172="","",IF(AND($E172&gt;0,LOWER($F172)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G172&lt;&gt;"",$I172=""),"направлено, но подтверждение направления не указано",IF($K172="","Отметьте включение копии в перечень приложений.",IF($L172="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="173">
@@ -5111,8 +4949,7 @@
         <v/>
       </c>
       <c r="M173" s="13">
-        <f>IF($B173="","",IF(AND($E173&gt;0,LOWER($F173)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G173&lt;&gt;"",$I173=""),"направлено, но подтверждение направления не указано",IF($K173="","отметьте, идёт ли копия в пакет",IF($L173="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B173="","",IF(AND($E173&gt;0,LOWER($F173)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G173&lt;&gt;"",$I173=""),"направлено, но подтверждение направления не указано",IF($K173="","Отметьте включение копии в перечень приложений.",IF($L173="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="174">
@@ -5135,8 +4972,7 @@
         <v/>
       </c>
       <c r="M174" s="13">
-        <f>IF($B174="","",IF(AND($E174&gt;0,LOWER($F174)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G174&lt;&gt;"",$I174=""),"направлено, но подтверждение направления не указано",IF($K174="","отметьте, идёт ли копия в пакет",IF($L174="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B174="","",IF(AND($E174&gt;0,LOWER($F174)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G174&lt;&gt;"",$I174=""),"направлено, но подтверждение направления не указано",IF($K174="","Отметьте включение копии в перечень приложений.",IF($L174="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="175">
@@ -5159,8 +4995,7 @@
         <v/>
       </c>
       <c r="M175" s="13">
-        <f>IF($B175="","",IF(AND($E175&gt;0,LOWER($F175)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G175&lt;&gt;"",$I175=""),"направлено, но подтверждение направления не указано",IF($K175="","отметьте, идёт ли копия в пакет",IF($L175="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B175="","",IF(AND($E175&gt;0,LOWER($F175)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G175&lt;&gt;"",$I175=""),"направлено, но подтверждение направления не указано",IF($K175="","Отметьте включение копии в перечень приложений.",IF($L175="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="176">
@@ -5183,8 +5018,7 @@
         <v/>
       </c>
       <c r="M176" s="13">
-        <f>IF($B176="","",IF(AND($E176&gt;0,LOWER($F176)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G176&lt;&gt;"",$I176=""),"направлено, но подтверждение направления не указано",IF($K176="","отметьте, идёт ли копия в пакет",IF($L176="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B176="","",IF(AND($E176&gt;0,LOWER($F176)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G176&lt;&gt;"",$I176=""),"направлено, но подтверждение направления не указано",IF($K176="","Отметьте включение копии в перечень приложений.",IF($L176="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="177">
@@ -5207,8 +5041,7 @@
         <v/>
       </c>
       <c r="M177" s="13">
-        <f>IF($B177="","",IF(AND($E177&gt;0,LOWER($F177)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G177&lt;&gt;"",$I177=""),"направлено, но подтверждение направления не указано",IF($K177="","отметьте, идёт ли копия в пакет",IF($L177="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B177="","",IF(AND($E177&gt;0,LOWER($F177)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G177&lt;&gt;"",$I177=""),"направлено, но подтверждение направления не указано",IF($K177="","Отметьте включение копии в перечень приложений.",IF($L177="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="178">
@@ -5231,8 +5064,7 @@
         <v/>
       </c>
       <c r="M178" s="13">
-        <f>IF($B178="","",IF(AND($E178&gt;0,LOWER($F178)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G178&lt;&gt;"",$I178=""),"направлено, но подтверждение направления не указано",IF($K178="","отметьте, идёт ли копия в пакет",IF($L178="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B178="","",IF(AND($E178&gt;0,LOWER($F178)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G178&lt;&gt;"",$I178=""),"направлено, но подтверждение направления не указано",IF($K178="","Отметьте включение копии в перечень приложений.",IF($L178="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="179">
@@ -5255,8 +5087,7 @@
         <v/>
       </c>
       <c r="M179" s="13">
-        <f>IF($B179="","",IF(AND($E179&gt;0,LOWER($F179)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G179&lt;&gt;"",$I179=""),"направлено, но подтверждение направления не указано",IF($K179="","отметьте, идёт ли копия в пакет",IF($L179="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B179="","",IF(AND($E179&gt;0,LOWER($F179)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G179&lt;&gt;"",$I179=""),"направлено, но подтверждение направления не указано",IF($K179="","Отметьте включение копии в перечень приложений.",IF($L179="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="180">
@@ -5279,8 +5110,7 @@
         <v/>
       </c>
       <c r="M180" s="13">
-        <f>IF($B180="","",IF(AND($E180&gt;0,LOWER($F180)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G180&lt;&gt;"",$I180=""),"направлено, но подтверждение направления не указано",IF($K180="","отметьте, идёт ли копия в пакет",IF($L180="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B180="","",IF(AND($E180&gt;0,LOWER($F180)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G180&lt;&gt;"",$I180=""),"направлено, но подтверждение направления не указано",IF($K180="","Отметьте включение копии в перечень приложений.",IF($L180="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="181">
@@ -5303,8 +5133,7 @@
         <v/>
       </c>
       <c r="M181" s="13">
-        <f>IF($B181="","",IF(AND($E181&gt;0,LOWER($F181)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G181&lt;&gt;"",$I181=""),"направлено, но подтверждение направления не указано",IF($K181="","отметьте, идёт ли копия в пакет",IF($L181="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B181="","",IF(AND($E181&gt;0,LOWER($F181)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G181&lt;&gt;"",$I181=""),"направлено, но подтверждение направления не указано",IF($K181="","Отметьте включение копии в перечень приложений.",IF($L181="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="182">
@@ -5327,8 +5156,7 @@
         <v/>
       </c>
       <c r="M182" s="13">
-        <f>IF($B182="","",IF(AND($E182&gt;0,LOWER($F182)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G182&lt;&gt;"",$I182=""),"направлено, но подтверждение направления не указано",IF($K182="","отметьте, идёт ли копия в пакет",IF($L182="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B182="","",IF(AND($E182&gt;0,LOWER($F182)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G182&lt;&gt;"",$I182=""),"направлено, но подтверждение направления не указано",IF($K182="","Отметьте включение копии в перечень приложений.",IF($L182="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="183">
@@ -5351,8 +5179,7 @@
         <v/>
       </c>
       <c r="M183" s="13">
-        <f>IF($B183="","",IF(AND($E183&gt;0,LOWER($F183)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G183&lt;&gt;"",$I183=""),"направлено, но подтверждение направления не указано",IF($K183="","отметьте, идёт ли копия в пакет",IF($L183="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B183="","",IF(AND($E183&gt;0,LOWER($F183)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G183&lt;&gt;"",$I183=""),"направлено, но подтверждение направления не указано",IF($K183="","Отметьте включение копии в перечень приложений.",IF($L183="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="184">
@@ -5375,8 +5202,7 @@
         <v/>
       </c>
       <c r="M184" s="13">
-        <f>IF($B184="","",IF(AND($E184&gt;0,LOWER($F184)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G184&lt;&gt;"",$I184=""),"направлено, но подтверждение направления не указано",IF($K184="","отметьте, идёт ли копия в пакет",IF($L184="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B184="","",IF(AND($E184&gt;0,LOWER($F184)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G184&lt;&gt;"",$I184=""),"направлено, но подтверждение направления не указано",IF($K184="","Отметьте включение копии в перечень приложений.",IF($L184="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="185">
@@ -5399,8 +5225,7 @@
         <v/>
       </c>
       <c r="M185" s="13">
-        <f>IF($B185="","",IF(AND($E185&gt;0,LOWER($F185)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G185&lt;&gt;"",$I185=""),"направлено, но подтверждение направления не указано",IF($K185="","отметьте, идёт ли копия в пакет",IF($L185="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B185="","",IF(AND($E185&gt;0,LOWER($F185)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G185&lt;&gt;"",$I185=""),"направлено, но подтверждение направления не указано",IF($K185="","Отметьте включение копии в перечень приложений.",IF($L185="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="186">
@@ -5423,8 +5248,7 @@
         <v/>
       </c>
       <c r="M186" s="13">
-        <f>IF($B186="","",IF(AND($E186&gt;0,LOWER($F186)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G186&lt;&gt;"",$I186=""),"направлено, но подтверждение направления не указано",IF($K186="","отметьте, идёт ли копия в пакет",IF($L186="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B186="","",IF(AND($E186&gt;0,LOWER($F186)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G186&lt;&gt;"",$I186=""),"направлено, но подтверждение направления не указано",IF($K186="","Отметьте включение копии в перечень приложений.",IF($L186="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="187">
@@ -5447,8 +5271,7 @@
         <v/>
       </c>
       <c r="M187" s="13">
-        <f>IF($B187="","",IF(AND($E187&gt;0,LOWER($F187)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G187&lt;&gt;"",$I187=""),"направлено, но подтверждение направления не указано",IF($K187="","отметьте, идёт ли копия в пакет",IF($L187="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B187="","",IF(AND($E187&gt;0,LOWER($F187)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G187&lt;&gt;"",$I187=""),"направлено, но подтверждение направления не указано",IF($K187="","Отметьте включение копии в перечень приложений.",IF($L187="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="188">
@@ -5471,8 +5294,7 @@
         <v/>
       </c>
       <c r="M188" s="13">
-        <f>IF($B188="","",IF(AND($E188&gt;0,LOWER($F188)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G188&lt;&gt;"",$I188=""),"направлено, но подтверждение направления не указано",IF($K188="","отметьте, идёт ли копия в пакет",IF($L188="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B188="","",IF(AND($E188&gt;0,LOWER($F188)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G188&lt;&gt;"",$I188=""),"направлено, но подтверждение направления не указано",IF($K188="","Отметьте включение копии в перечень приложений.",IF($L188="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="189">
@@ -5495,8 +5317,7 @@
         <v/>
       </c>
       <c r="M189" s="13">
-        <f>IF($B189="","",IF(AND($E189&gt;0,LOWER($F189)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G189&lt;&gt;"",$I189=""),"направлено, но подтверждение направления не указано",IF($K189="","отметьте, идёт ли копия в пакет",IF($L189="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B189="","",IF(AND($E189&gt;0,LOWER($F189)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G189&lt;&gt;"",$I189=""),"направлено, но подтверждение направления не указано",IF($K189="","Отметьте включение копии в перечень приложений.",IF($L189="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="190">
@@ -5519,8 +5340,7 @@
         <v/>
       </c>
       <c r="M190" s="13">
-        <f>IF($B190="","",IF(AND($E190&gt;0,LOWER($F190)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G190&lt;&gt;"",$I190=""),"направлено, но подтверждение направления не указано",IF($K190="","отметьте, идёт ли копия в пакет",IF($L190="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B190="","",IF(AND($E190&gt;0,LOWER($F190)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G190&lt;&gt;"",$I190=""),"направлено, но подтверждение направления не указано",IF($K190="","Отметьте включение копии в перечень приложений.",IF($L190="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="191">
@@ -5543,8 +5363,7 @@
         <v/>
       </c>
       <c r="M191" s="13">
-        <f>IF($B191="","",IF(AND($E191&gt;0,LOWER($F191)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G191&lt;&gt;"",$I191=""),"направлено, но подтверждение направления не указано",IF($K191="","отметьте, идёт ли копия в пакет",IF($L191="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B191="","",IF(AND($E191&gt;0,LOWER($F191)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G191&lt;&gt;"",$I191=""),"направлено, но подтверждение направления не указано",IF($K191="","Отметьте включение копии в перечень приложений.",IF($L191="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="192">
@@ -5567,8 +5386,7 @@
         <v/>
       </c>
       <c r="M192" s="13">
-        <f>IF($B192="","",IF(AND($E192&gt;0,LOWER($F192)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G192&lt;&gt;"",$I192=""),"направлено, но подтверждение направления не указано",IF($K192="","отметьте, идёт ли копия в пакет",IF($L192="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B192="","",IF(AND($E192&gt;0,LOWER($F192)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G192&lt;&gt;"",$I192=""),"направлено, но подтверждение направления не указано",IF($K192="","Отметьте включение копии в перечень приложений.",IF($L192="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="193">
@@ -5591,8 +5409,7 @@
         <v/>
       </c>
       <c r="M193" s="13">
-        <f>IF($B193="","",IF(AND($E193&gt;0,LOWER($F193)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G193&lt;&gt;"",$I193=""),"направлено, но подтверждение направления не указано",IF($K193="","отметьте, идёт ли копия в пакет",IF($L193="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B193="","",IF(AND($E193&gt;0,LOWER($F193)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G193&lt;&gt;"",$I193=""),"направлено, но подтверждение направления не указано",IF($K193="","Отметьте включение копии в перечень приложений.",IF($L193="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="194">
@@ -5615,8 +5432,7 @@
         <v/>
       </c>
       <c r="M194" s="13">
-        <f>IF($B194="","",IF(AND($E194&gt;0,LOWER($F194)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G194&lt;&gt;"",$I194=""),"направлено, но подтверждение направления не указано",IF($K194="","отметьте, идёт ли копия в пакет",IF($L194="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B194="","",IF(AND($E194&gt;0,LOWER($F194)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G194&lt;&gt;"",$I194=""),"направлено, но подтверждение направления не указано",IF($K194="","Отметьте включение копии в перечень приложений.",IF($L194="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="195">
@@ -5639,8 +5455,7 @@
         <v/>
       </c>
       <c r="M195" s="13">
-        <f>IF($B195="","",IF(AND($E195&gt;0,LOWER($F195)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G195&lt;&gt;"",$I195=""),"направлено, но подтверждение направления не указано",IF($K195="","отметьте, идёт ли копия в пакет",IF($L195="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B195="","",IF(AND($E195&gt;0,LOWER($F195)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G195&lt;&gt;"",$I195=""),"направлено, но подтверждение направления не указано",IF($K195="","Отметьте включение копии в перечень приложений.",IF($L195="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="196">
@@ -5663,8 +5478,7 @@
         <v/>
       </c>
       <c r="M196" s="13">
-        <f>IF($B196="","",IF(AND($E196&gt;0,LOWER($F196)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G196&lt;&gt;"",$I196=""),"направлено, но подтверждение направления не указано",IF($K196="","отметьте, идёт ли копия в пакет",IF($L196="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B196="","",IF(AND($E196&gt;0,LOWER($F196)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G196&lt;&gt;"",$I196=""),"направлено, но подтверждение направления не указано",IF($K196="","Отметьте включение копии в перечень приложений.",IF($L196="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="197">
@@ -5687,8 +5501,7 @@
         <v/>
       </c>
       <c r="M197" s="13">
-        <f>IF($B197="","",IF(AND($E197&gt;0,LOWER($F197)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G197&lt;&gt;"",$I197=""),"направлено, но подтверждение направления не указано",IF($K197="","отметьте, идёт ли копия в пакет",IF($L197="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B197="","",IF(AND($E197&gt;0,LOWER($F197)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G197&lt;&gt;"",$I197=""),"направлено, но подтверждение направления не указано",IF($K197="","Отметьте включение копии в перечень приложений.",IF($L197="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="198">
@@ -5711,8 +5524,7 @@
         <v/>
       </c>
       <c r="M198" s="13">
-        <f>IF($B198="","",IF(AND($E198&gt;0,LOWER($F198)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G198&lt;&gt;"",$I198=""),"направлено, но подтверждение направления не указано",IF($K198="","отметьте, идёт ли копия в пакет",IF($L198="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B198="","",IF(AND($E198&gt;0,LOWER($F198)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G198&lt;&gt;"",$I198=""),"направлено, но подтверждение направления не указано",IF($K198="","Отметьте включение копии в перечень приложений.",IF($L198="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="199">
@@ -5735,8 +5547,7 @@
         <v/>
       </c>
       <c r="M199" s="13">
-        <f>IF($B199="","",IF(AND($E199&gt;0,LOWER($F199)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G199&lt;&gt;"",$I199=""),"направлено, но подтверждение направления не указано",IF($K199="","отметьте, идёт ли копия в пакет",IF($L199="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B199="","",IF(AND($E199&gt;0,LOWER($F199)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G199&lt;&gt;"",$I199=""),"направлено, но подтверждение направления не указано",IF($K199="","Отметьте включение копии в перечень приложений.",IF($L199="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="200">
@@ -5759,8 +5570,7 @@
         <v/>
       </c>
       <c r="M200" s="13">
-        <f>IF($B200="","",IF(AND($E200&gt;0,LOWER($F200)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G200&lt;&gt;"",$I200=""),"направлено, но подтверждение направления не указано",IF($K200="","отметьте, идёт ли копия в пакет",IF($L200="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B200="","",IF(AND($E200&gt;0,LOWER($F200)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G200&lt;&gt;"",$I200=""),"направлено, но подтверждение направления не указано",IF($K200="","Отметьте включение копии в перечень приложений.",IF($L200="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="201">
@@ -5783,8 +5593,7 @@
         <v/>
       </c>
       <c r="M201" s="13">
-        <f>IF($B201="","",IF(AND($E201&gt;0,LOWER($F201)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G201&lt;&gt;"",$I201=""),"направлено, но подтверждение направления не указано",IF($K201="","отметьте, идёт ли копия в пакет",IF($L201="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B201="","",IF(AND($E201&gt;0,LOWER($F201)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G201&lt;&gt;"",$I201=""),"направлено, но подтверждение направления не указано",IF($K201="","Отметьте включение копии в перечень приложений.",IF($L201="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="202">
@@ -5807,8 +5616,7 @@
         <v/>
       </c>
       <c r="M202" s="13">
-        <f>IF($B202="","",IF(AND($E202&gt;0,LOWER($F202)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G202&lt;&gt;"",$I202=""),"направлено, но подтверждение направления не указано",IF($K202="","отметьте, идёт ли копия в пакет",IF($L202="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B202="","",IF(AND($E202&gt;0,LOWER($F202)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G202&lt;&gt;"",$I202=""),"направлено, но подтверждение направления не указано",IF($K202="","Отметьте включение копии в перечень приложений.",IF($L202="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="203">
@@ -5831,14 +5639,13 @@
         <v/>
       </c>
       <c r="M203" s="13">
-        <f>IF($B203="","",IF(AND($E203&gt;0,LOWER($F203)&lt;&gt;"да"),"сумма есть, подписи обеих сторон нет — отдельно обсудите с юристом",IF(AND($G203&lt;&gt;"",$I203=""),"направлено, но подтверждение направления не указано",IF($K203="","отметьте, идёт ли копия в пакет",IF($L203="после принятия заявления","после принятия заявления — возможно текущий платёж (ст. 5), к юристу","")))))</f>
-        <v/>
+        <f>IF($B203="","",IF(AND($E203&gt;0,LOWER($F203)&lt;&gt;"да"),"Акт не подписан обеими сторонами: проверьте подтверждения выполнения и сдачи.",IF(AND($G203&lt;&gt;"",$I203=""),"направлено, но подтверждение направления не указано",IF($K203="","Отметьте включение копии в перечень приложений.",IF($L203="после принятия заявления","Проверьте признаки текущего платежа по статье 5 Закона № 127-ФЗ.","")))))</f>
       </c>
     </row>
     <row r="205" ht="46" customHeight="1">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>Колонка «Проверка» должна быть пустой во всех заполненных строках. Непустая строка — это не запрет подавать, а вопрос, ответ на который лучше знать до подачи, а не после.</t>
+          <t>Проверьте строки с замечанием в колонке «Проверка» по первичным документам до составления требования.</t>
         </is>
       </c>
     </row>
@@ -5848,11 +5655,12 @@
     <mergeCell ref="A205:M205"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168 F169 F170 F171 F172 F173 F174 F175 F176 F177 F178 F179 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F191 F192 F193 F194 F195 F196 F197 F198 F199 F200 F201 F202 F203 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69 K70 K71 K72 K73 K74 K75 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K86 K87 K88 K89 K90 K91 K92 K93 K94 K95 K96 K97 K98 K99 K100 K101 K102 K103 K104 K105 K106 K107 K108 K109 K110 K111 K112 K113 K114 K115 K116 K117 K118 K119 K120 K121 K122 K123 K124 K125 K126 K127 K128 K129 K130 K131 K132 K133 K134 K135 K136 K137 K138 K139 K140 K141 K142 K143 K144 K145 K146 K147 K148 K149 K150 K151 K152 K153 K154 K155 K156 K157 K158 K159 K160 K161 K162 K163 K164 K165 K166 K167 K168 K169 K170 K171 K172 K173 K174 K175 K176 K177 K178 K179 K180 K181 K182 K183 K184 K185 K186 K187 K188 K189 K190 K191 K192 K193 K194 K195 K196 K197 K198 K199 K200 K201 K202 K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Введите «да» или «нет»" type="list">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168 F169 F170 F171 F172 F173 F174 F175 F176 F177 F178 F179 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F191 F192 F193 F194 F195 F196 F197 F198 F199 F200 F201 F202 F203 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 K52 K53 K54 K55 K56 K57 K58 K59 K60 K61 K62 K63 K64 K65 K66 K67 K68 K69 K70 K71 K72 K73 K74 K75 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K86 K87 K88 K89 K90 K91 K92 K93 K94 K95 K96 K97 K98 K99 K100 K101 K102 K103 K104 K105 K106 K107 K108 K109 K110 K111 K112 K113 K114 K115 K116 K117 K118 K119 K120 K121 K122 K123 K124 K125 K126 K127 K128 K129 K130 K131 K132 K133 K134 K135 K136 K137 K138 K139 K140 K141 K142 K143 K144 K145 K146 K147 K148 K149 K150 K151 K152 K153 K154 K155 K156 K157 K158 K159 K160 K161 K162 K163 K164 K165 K166 K167 K168 K169 K170 K171 K172 K173 K174 K175 K176 K177 K178 K179 K180 K181 K182 K183 K184 K185 K186 K187 K188 K189 K190 K191 K192 K193 K194 K195 K196 K197 K198 K199 K200 K201 K202 K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Введите «да» или «нет»" type="list">
       <formula1>"да,нет"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5860,7 +5668,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5870,17 +5678,17 @@
     <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Итоги: что собрано и что осталось</t>
+          <t xml:space="preserve">Итоги комплектования документов</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Считается по листу «Реестр документов». Ничего вводить не нужно.</t>
+          <t xml:space="preserve">Показатели формируются по листу «Реестр документов». Сверьте их с расчётом требования и перечнем приложений.</t>
         </is>
       </c>
     </row>
@@ -5976,11 +5784,11 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Должно быть ноль. Каждая непустая строка — вопрос, который лучше закрыть до подачи</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t xml:space="preserve">Проверьте каждую отмеченную строку и устраните ошибки до подачи заявления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24.0" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Направлено, но подтверждение не указано</t>
@@ -5992,7 +5800,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Письмо без подтверждения отправки доказательством не является</t>
+          <t xml:space="preserve">По каждой отмеченной строке проверьте реквизиты, даты и подтверждающие документы до подачи заявления.</t>
         </is>
       </c>
     </row>
@@ -6011,35 +5819,35 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Что эти суммы не означают</t>
+          <t xml:space="preserve">Сопоставление с расчётом требования</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>— Не размер требования. Требование считается отдельно, и основной долг учитывается отдельно от финансовых санкций (ст. 137 Закона о банкротстве). Сумма из этого файла — рабочий ориентир, чтобы сверить, всё ли учтено.</t>
+          <t xml:space="preserve">Основной долг и финансовые санкции рассчитайте раздельно с учётом статьи 137 Закона № 127-ФЗ. Суммы реестра документов используйте для сверки полноты исходных данных.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>— Не сумму, которую вы получите. Включение в реестр даёт право на долю в том, что удастся собрать, а не платёж. В банкротстве требование чаще удовлетворяется частично или не удовлетворяется вовсе.</t>
+          <t xml:space="preserve">После установления требования контролируйте расчёты по судебным актам, реестру кредиторов и сообщениям управляющего. Фактическое удовлетворение зависит от процедуры и имущества должника.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>— Не квалификацию требований. Деление по дате принятия заявления сделано, чтобы было с чем идти к юристу; момент возникновения обязательства не всегда совпадает с датой документа.</t>
+          <t>Разделение по дате принятия заявления служит для сверки; характер требования определяйте по дате возникновения обязательства и применимому закону.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>— Не заменяет заявление. Требование включается в реестр по судебному акту, а не по письму управляющему и не по заполненной таблице.</t>
+          <t>Заявление о включении требования подаётся в арбитражный суд в установленном порядке.</t>
         </is>
       </c>
     </row>
@@ -6052,6 +5860,7 @@
     <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6059,7 +5868,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6089,7 +5898,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Здесь показан формат ввода, а не ваш случай. Наименования, номера и даты вымышленные. Ничего отсюда не переносите в свой файл и тем более в документы.</t>
+          <t xml:space="preserve">Учебный пример показывает заполнение реквизитов и строк реестра. Рабочие сведения внесите по документам своего объекта и должника.</t>
         </is>
       </c>
     </row>
@@ -6187,7 +5996,7 @@
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Обратите внимание: в строке «Дата, до которой требование должно быть заявлено» в примере стоит не число, а описание. Число сюда ставите вы по результату проверки действующей редакции — готового значения нет ни в примере, ни в формулах.</t>
+          <t xml:space="preserve">Предельную дату заявления требования определите по судебному акту, публикации и применимой норме. Зафиксируйте расчёт срока и дату проверки.</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6007,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="26.4" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>№</t>
@@ -6246,7 +6055,7 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Где лежит оригинал</t>
+          <t xml:space="preserve">Место хранения оригинала</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
@@ -6492,7 +6301,7 @@
     <row r="22" ht="46" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Четвёртая строка примера датирована позже даты принятия заявления из примера выше — колонка «Период» отметит её как «после принятия заявления», а «Проверка» напомнит, что это возможный текущий платёж (ст. 5 Закона о банкротстве) и что квалифицирует его юрист, а не таблица.</t>
+          <t>Для документа после принятия заявления отдельно проверьте признаки текущего платежа и основание обязательства.</t>
         </is>
       </c>
     </row>
@@ -6510,5 +6319,6 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>